--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800263</v>
+        <v>124800264</v>
       </c>
       <c r="B2" t="n">
-        <v>74901</v>
+        <v>91026</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441519</v>
+        <v>441499</v>
       </c>
       <c r="R2" t="n">
-        <v>6999856</v>
+        <v>6999862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800273</v>
+        <v>124800288</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441403</v>
+        <v>441172</v>
       </c>
       <c r="R3" t="n">
-        <v>6999822</v>
+        <v>6999861</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800289</v>
+        <v>124800257</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441172</v>
+        <v>441670</v>
       </c>
       <c r="R4" t="n">
-        <v>6999878</v>
+        <v>6999866</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800290</v>
+        <v>124800261</v>
       </c>
       <c r="B5" t="n">
-        <v>74906</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441172</v>
+        <v>441557</v>
       </c>
       <c r="R5" t="n">
-        <v>6999861</v>
+        <v>6999865</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800257</v>
+        <v>124800289</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441670</v>
+        <v>441172</v>
       </c>
       <c r="R6" t="n">
-        <v>6999866</v>
+        <v>6999878</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800292</v>
+        <v>124800278</v>
       </c>
       <c r="B7" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441167</v>
+        <v>441332</v>
       </c>
       <c r="R7" t="n">
-        <v>6999862</v>
+        <v>6999837</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800262</v>
+        <v>124800283</v>
       </c>
       <c r="B8" t="n">
-        <v>77753</v>
+        <v>96354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>314</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441527</v>
+        <v>441246</v>
       </c>
       <c r="R8" t="n">
-        <v>6999858</v>
+        <v>6999794</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800279</v>
+        <v>124800262</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>77753</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441280</v>
+        <v>441527</v>
       </c>
       <c r="R9" t="n">
-        <v>6999989</v>
+        <v>6999858</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800276</v>
+        <v>124800273</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441381</v>
+        <v>441403</v>
       </c>
       <c r="R10" t="n">
-        <v>7000012</v>
+        <v>6999822</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800284</v>
+        <v>124800277</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441196</v>
+        <v>441332</v>
       </c>
       <c r="R11" t="n">
-        <v>6999904</v>
+        <v>6999837</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800270</v>
+        <v>124800285</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>74906</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441439</v>
+        <v>441184</v>
       </c>
       <c r="R12" t="n">
-        <v>6999872</v>
+        <v>6999878</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800288</v>
+        <v>124800284</v>
       </c>
       <c r="B13" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441172</v>
+        <v>441196</v>
       </c>
       <c r="R13" t="n">
-        <v>6999861</v>
+        <v>6999904</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800277</v>
+        <v>124800260</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441332</v>
+        <v>441560</v>
       </c>
       <c r="R14" t="n">
-        <v>6999837</v>
+        <v>6999870</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800261</v>
+        <v>124800269</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>91700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2091,16 +2091,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441557</v>
+        <v>441442</v>
       </c>
       <c r="R15" t="n">
-        <v>6999865</v>
+        <v>6999893</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,12 +2138,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2159,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800281</v>
+        <v>124800263</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2203,10 +2212,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441261</v>
+        <v>441519</v>
       </c>
       <c r="R16" t="n">
-        <v>6999970</v>
+        <v>6999856</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2274,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800258</v>
+        <v>124800286</v>
       </c>
       <c r="B17" t="n">
         <v>91030</v>
@@ -2309,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441578</v>
+        <v>441175</v>
       </c>
       <c r="R17" t="n">
-        <v>6999868</v>
+        <v>6999877</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800278</v>
+        <v>124800267</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2396,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2415,10 +2424,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441332</v>
+        <v>441444</v>
       </c>
       <c r="R18" t="n">
-        <v>6999837</v>
+        <v>6999902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800285</v>
+        <v>124800292</v>
       </c>
       <c r="B19" t="n">
-        <v>74906</v>
+        <v>82597</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2502,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2521,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441184</v>
+        <v>441167</v>
       </c>
       <c r="R19" t="n">
-        <v>6999878</v>
+        <v>6999862</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2592,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800283</v>
+        <v>124800291</v>
       </c>
       <c r="B20" t="n">
-        <v>96354</v>
+        <v>74885</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2604,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>6439</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2627,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441246</v>
+        <v>441167</v>
       </c>
       <c r="R20" t="n">
-        <v>6999794</v>
+        <v>6999845</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800264</v>
+        <v>124800274</v>
       </c>
       <c r="B21" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2714,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2733,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441499</v>
+        <v>441388</v>
       </c>
       <c r="R21" t="n">
-        <v>6999862</v>
+        <v>6999825</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2804,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800286</v>
+        <v>124800282</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>96354</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2820,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2839,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441175</v>
+        <v>441251</v>
       </c>
       <c r="R22" t="n">
-        <v>6999877</v>
+        <v>6999814</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800282</v>
+        <v>124800281</v>
       </c>
       <c r="B23" t="n">
-        <v>96354</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2917,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2945,10 +2954,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441251</v>
+        <v>441261</v>
       </c>
       <c r="R23" t="n">
-        <v>6999814</v>
+        <v>6999970</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800287</v>
+        <v>124800258</v>
       </c>
       <c r="B24" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,25 +3028,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3051,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441173</v>
+        <v>441578</v>
       </c>
       <c r="R24" t="n">
-        <v>6999874</v>
+        <v>6999868</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,10 +3122,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800267</v>
+        <v>124800276</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3129,21 +3138,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3157,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441444</v>
+        <v>441381</v>
       </c>
       <c r="R25" t="n">
-        <v>6999902</v>
+        <v>7000012</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800275</v>
+        <v>124800266</v>
       </c>
       <c r="B26" t="n">
-        <v>91026</v>
+        <v>74901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3235,21 +3244,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3263,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441386</v>
+        <v>441484</v>
       </c>
       <c r="R26" t="n">
-        <v>6999830</v>
+        <v>6999855</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800291</v>
+        <v>124800279</v>
       </c>
       <c r="B27" t="n">
-        <v>74885</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3337,25 +3346,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3369,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441167</v>
+        <v>441280</v>
       </c>
       <c r="R27" t="n">
-        <v>6999845</v>
+        <v>6999989</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800269</v>
+        <v>124800287</v>
       </c>
       <c r="B28" t="n">
-        <v>91700</v>
+        <v>79920</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3447,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3469,19 +3478,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441442</v>
+        <v>441173</v>
       </c>
       <c r="R28" t="n">
-        <v>6999893</v>
+        <v>6999874</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3516,18 +3522,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800260</v>
+        <v>124800290</v>
       </c>
       <c r="B29" t="n">
-        <v>91299</v>
+        <v>74906</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1467</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441560</v>
+        <v>441172</v>
       </c>
       <c r="R29" t="n">
-        <v>6999870</v>
+        <v>6999861</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800266</v>
+        <v>124800275</v>
       </c>
       <c r="B30" t="n">
-        <v>74901</v>
+        <v>91026</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3668,21 +3668,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441484</v>
+        <v>441386</v>
       </c>
       <c r="R30" t="n">
-        <v>6999855</v>
+        <v>6999830</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800274</v>
+        <v>124800270</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441388</v>
+        <v>441439</v>
       </c>
       <c r="R31" t="n">
-        <v>6999825</v>
+        <v>6999872</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800264</v>
+        <v>124800285</v>
       </c>
       <c r="B2" t="n">
-        <v>91026</v>
+        <v>74906</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441499</v>
+        <v>441184</v>
       </c>
       <c r="R2" t="n">
-        <v>6999862</v>
+        <v>6999878</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800288</v>
+        <v>124800263</v>
       </c>
       <c r="B3" t="n">
         <v>74901</v>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441172</v>
+        <v>441519</v>
       </c>
       <c r="R3" t="n">
-        <v>6999861</v>
+        <v>6999856</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800257</v>
+        <v>124800262</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>77753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441670</v>
+        <v>441527</v>
       </c>
       <c r="R4" t="n">
-        <v>6999866</v>
+        <v>6999858</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800261</v>
+        <v>124800291</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>74885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441557</v>
+        <v>441167</v>
       </c>
       <c r="R5" t="n">
-        <v>6999865</v>
+        <v>6999845</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800289</v>
+        <v>124800281</v>
       </c>
       <c r="B6" t="n">
         <v>91030</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441172</v>
+        <v>441261</v>
       </c>
       <c r="R6" t="n">
-        <v>6999878</v>
+        <v>6999970</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800278</v>
+        <v>124800277</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800283</v>
+        <v>124800270</v>
       </c>
       <c r="B8" t="n">
-        <v>96354</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441246</v>
+        <v>441439</v>
       </c>
       <c r="R8" t="n">
-        <v>6999794</v>
+        <v>6999872</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800262</v>
+        <v>124800274</v>
       </c>
       <c r="B9" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441527</v>
+        <v>441388</v>
       </c>
       <c r="R9" t="n">
-        <v>6999858</v>
+        <v>6999825</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800273</v>
+        <v>124800287</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441403</v>
+        <v>441173</v>
       </c>
       <c r="R10" t="n">
-        <v>6999822</v>
+        <v>6999874</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800277</v>
+        <v>124800283</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441332</v>
+        <v>441246</v>
       </c>
       <c r="R11" t="n">
-        <v>6999837</v>
+        <v>6999794</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800285</v>
+        <v>124800267</v>
       </c>
       <c r="B12" t="n">
-        <v>74906</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441184</v>
+        <v>441444</v>
       </c>
       <c r="R12" t="n">
-        <v>6999878</v>
+        <v>6999902</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800284</v>
+        <v>124800264</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441196</v>
+        <v>441499</v>
       </c>
       <c r="R13" t="n">
-        <v>6999904</v>
+        <v>6999862</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800269</v>
+        <v>124800266</v>
       </c>
       <c r="B15" t="n">
-        <v>91700</v>
+        <v>74901</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2091,19 +2091,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441442</v>
+        <v>441484</v>
       </c>
       <c r="R15" t="n">
-        <v>6999893</v>
+        <v>6999855</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,18 +2135,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2168,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800263</v>
+        <v>124800286</v>
       </c>
       <c r="B16" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2212,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441519</v>
+        <v>441175</v>
       </c>
       <c r="R16" t="n">
-        <v>6999856</v>
+        <v>6999877</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800286</v>
+        <v>124800273</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2318,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441175</v>
+        <v>441403</v>
       </c>
       <c r="R17" t="n">
-        <v>6999877</v>
+        <v>6999822</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800267</v>
+        <v>124800278</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2396,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2424,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441444</v>
+        <v>441332</v>
       </c>
       <c r="R18" t="n">
-        <v>6999902</v>
+        <v>6999837</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800292</v>
+        <v>124800282</v>
       </c>
       <c r="B19" t="n">
-        <v>82597</v>
+        <v>96354</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2502,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2530,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441167</v>
+        <v>441251</v>
       </c>
       <c r="R19" t="n">
-        <v>6999862</v>
+        <v>6999814</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800291</v>
+        <v>124800289</v>
       </c>
       <c r="B20" t="n">
-        <v>74885</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2636,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441167</v>
+        <v>441172</v>
       </c>
       <c r="R20" t="n">
-        <v>6999845</v>
+        <v>6999878</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,7 +2689,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800274</v>
+        <v>124800279</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2742,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441388</v>
+        <v>441280</v>
       </c>
       <c r="R21" t="n">
-        <v>6999825</v>
+        <v>6999989</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800282</v>
+        <v>124800292</v>
       </c>
       <c r="B22" t="n">
-        <v>96354</v>
+        <v>82597</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2820,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2848,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441251</v>
+        <v>441167</v>
       </c>
       <c r="R22" t="n">
-        <v>6999814</v>
+        <v>6999862</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800281</v>
+        <v>124800290</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>74906</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2926,21 +2917,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2954,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441261</v>
+        <v>441172</v>
       </c>
       <c r="R23" t="n">
-        <v>6999970</v>
+        <v>6999861</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800258</v>
+        <v>124800284</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3032,21 +3023,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3060,10 +3051,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441578</v>
+        <v>441196</v>
       </c>
       <c r="R24" t="n">
-        <v>6999868</v>
+        <v>6999904</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800276</v>
+        <v>124800288</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3138,21 +3129,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3166,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441381</v>
+        <v>441172</v>
       </c>
       <c r="R25" t="n">
-        <v>7000012</v>
+        <v>6999861</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800266</v>
+        <v>124800261</v>
       </c>
       <c r="B26" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,21 +3235,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3272,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441484</v>
+        <v>441557</v>
       </c>
       <c r="R26" t="n">
-        <v>6999855</v>
+        <v>6999865</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800279</v>
+        <v>124800257</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3350,21 +3341,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3378,10 +3369,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441280</v>
+        <v>441670</v>
       </c>
       <c r="R27" t="n">
-        <v>6999989</v>
+        <v>6999866</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800287</v>
+        <v>124800258</v>
       </c>
       <c r="B28" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3452,25 +3443,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3484,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441173</v>
+        <v>441578</v>
       </c>
       <c r="R28" t="n">
-        <v>6999874</v>
+        <v>6999868</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800290</v>
+        <v>124800275</v>
       </c>
       <c r="B29" t="n">
-        <v>74906</v>
+        <v>91026</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3562,21 +3553,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3590,10 +3581,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441172</v>
+        <v>441386</v>
       </c>
       <c r="R29" t="n">
-        <v>6999861</v>
+        <v>6999830</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800275</v>
+        <v>124800276</v>
       </c>
       <c r="B30" t="n">
-        <v>91026</v>
+        <v>91030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3668,21 +3659,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3696,10 +3687,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441386</v>
+        <v>441381</v>
       </c>
       <c r="R30" t="n">
-        <v>6999830</v>
+        <v>7000012</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,10 +3749,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800270</v>
+        <v>124800269</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>91700</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3770,25 +3761,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3796,16 +3787,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441439</v>
+        <v>441442</v>
       </c>
       <c r="R31" t="n">
-        <v>6999872</v>
+        <v>6999893</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3840,12 +3834,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800262</v>
+        <v>124800291</v>
       </c>
       <c r="B4" t="n">
-        <v>77753</v>
+        <v>74885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441527</v>
+        <v>441167</v>
       </c>
       <c r="R4" t="n">
-        <v>6999858</v>
+        <v>6999845</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800291</v>
+        <v>124800281</v>
       </c>
       <c r="B5" t="n">
-        <v>74885</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441167</v>
+        <v>441261</v>
       </c>
       <c r="R5" t="n">
-        <v>6999845</v>
+        <v>6999970</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800281</v>
+        <v>124800262</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>77753</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441261</v>
+        <v>441527</v>
       </c>
       <c r="R6" t="n">
-        <v>6999970</v>
+        <v>6999858</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800270</v>
+        <v>124800283</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>96354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441439</v>
+        <v>441246</v>
       </c>
       <c r="R8" t="n">
-        <v>6999872</v>
+        <v>6999794</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800274</v>
+        <v>124800270</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441388</v>
+        <v>441439</v>
       </c>
       <c r="R9" t="n">
-        <v>6999825</v>
+        <v>6999872</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800287</v>
+        <v>124800274</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441173</v>
+        <v>441388</v>
       </c>
       <c r="R10" t="n">
-        <v>6999874</v>
+        <v>6999825</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800283</v>
+        <v>124800287</v>
       </c>
       <c r="B11" t="n">
-        <v>96354</v>
+        <v>79920</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441246</v>
+        <v>441173</v>
       </c>
       <c r="R11" t="n">
-        <v>6999794</v>
+        <v>6999874</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800267</v>
+        <v>124800264</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441444</v>
+        <v>441499</v>
       </c>
       <c r="R12" t="n">
-        <v>6999902</v>
+        <v>6999862</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800264</v>
+        <v>124800267</v>
       </c>
       <c r="B13" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441499</v>
+        <v>441444</v>
       </c>
       <c r="R13" t="n">
-        <v>6999862</v>
+        <v>6999902</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800282</v>
+        <v>124800289</v>
       </c>
       <c r="B19" t="n">
-        <v>96354</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441251</v>
+        <v>441172</v>
       </c>
       <c r="R19" t="n">
-        <v>6999814</v>
+        <v>6999878</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800289</v>
+        <v>124800282</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>96354</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441172</v>
+        <v>441251</v>
       </c>
       <c r="R20" t="n">
-        <v>6999878</v>
+        <v>6999814</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800291</v>
+        <v>124800262</v>
       </c>
       <c r="B4" t="n">
-        <v>74885</v>
+        <v>77753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441167</v>
+        <v>441527</v>
       </c>
       <c r="R4" t="n">
-        <v>6999845</v>
+        <v>6999858</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800281</v>
+        <v>124800291</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>74885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441261</v>
+        <v>441167</v>
       </c>
       <c r="R5" t="n">
-        <v>6999970</v>
+        <v>6999845</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800262</v>
+        <v>124800281</v>
       </c>
       <c r="B6" t="n">
-        <v>77753</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>314</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441527</v>
+        <v>441261</v>
       </c>
       <c r="R6" t="n">
-        <v>6999858</v>
+        <v>6999970</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800285</v>
+        <v>124800260</v>
       </c>
       <c r="B2" t="n">
-        <v>74906</v>
+        <v>91299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441184</v>
+        <v>441560</v>
       </c>
       <c r="R2" t="n">
-        <v>6999878</v>
+        <v>6999870</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800263</v>
+        <v>124800257</v>
       </c>
       <c r="B3" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441519</v>
+        <v>441670</v>
       </c>
       <c r="R3" t="n">
-        <v>6999856</v>
+        <v>6999866</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800262</v>
+        <v>124800284</v>
       </c>
       <c r="B4" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441527</v>
+        <v>441196</v>
       </c>
       <c r="R4" t="n">
-        <v>6999858</v>
+        <v>6999904</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800291</v>
+        <v>124800266</v>
       </c>
       <c r="B5" t="n">
-        <v>74885</v>
+        <v>74901</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441167</v>
+        <v>441484</v>
       </c>
       <c r="R5" t="n">
-        <v>6999845</v>
+        <v>6999855</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800281</v>
+        <v>124800270</v>
       </c>
       <c r="B6" t="n">
         <v>91030</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441261</v>
+        <v>441439</v>
       </c>
       <c r="R6" t="n">
-        <v>6999970</v>
+        <v>6999872</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800277</v>
+        <v>124800274</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441332</v>
+        <v>441388</v>
       </c>
       <c r="R7" t="n">
-        <v>6999837</v>
+        <v>6999825</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800283</v>
+        <v>124800261</v>
       </c>
       <c r="B8" t="n">
-        <v>96354</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441246</v>
+        <v>441557</v>
       </c>
       <c r="R8" t="n">
-        <v>6999794</v>
+        <v>6999865</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800270</v>
+        <v>124800258</v>
       </c>
       <c r="B9" t="n">
         <v>91030</v>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441439</v>
+        <v>441578</v>
       </c>
       <c r="R9" t="n">
-        <v>6999872</v>
+        <v>6999868</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800274</v>
+        <v>124800278</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441388</v>
+        <v>441332</v>
       </c>
       <c r="R10" t="n">
-        <v>6999825</v>
+        <v>6999837</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800287</v>
+        <v>124800279</v>
       </c>
       <c r="B11" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441173</v>
+        <v>441280</v>
       </c>
       <c r="R11" t="n">
-        <v>6999874</v>
+        <v>6999989</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800264</v>
+        <v>124800292</v>
       </c>
       <c r="B12" t="n">
-        <v>91026</v>
+        <v>82597</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441499</v>
+        <v>441167</v>
       </c>
       <c r="R12" t="n">
         <v>6999862</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800267</v>
+        <v>124800277</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441444</v>
+        <v>441332</v>
       </c>
       <c r="R13" t="n">
-        <v>6999902</v>
+        <v>6999837</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800260</v>
+        <v>124800281</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441560</v>
+        <v>441261</v>
       </c>
       <c r="R14" t="n">
-        <v>6999870</v>
+        <v>6999970</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800266</v>
+        <v>124800282</v>
       </c>
       <c r="B15" t="n">
-        <v>74901</v>
+        <v>96354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441484</v>
+        <v>441251</v>
       </c>
       <c r="R15" t="n">
-        <v>6999855</v>
+        <v>6999814</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800286</v>
+        <v>124800287</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>79920</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441175</v>
+        <v>441173</v>
       </c>
       <c r="R16" t="n">
-        <v>6999877</v>
+        <v>6999874</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800273</v>
+        <v>124800263</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441403</v>
+        <v>441519</v>
       </c>
       <c r="R17" t="n">
-        <v>6999822</v>
+        <v>6999856</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800278</v>
+        <v>124800291</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>74885</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441332</v>
+        <v>441167</v>
       </c>
       <c r="R18" t="n">
-        <v>6999837</v>
+        <v>6999845</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800289</v>
+        <v>124800275</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>91026</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441172</v>
+        <v>441386</v>
       </c>
       <c r="R19" t="n">
-        <v>6999878</v>
+        <v>6999830</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800282</v>
+        <v>124800264</v>
       </c>
       <c r="B20" t="n">
-        <v>96354</v>
+        <v>91026</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441251</v>
+        <v>441499</v>
       </c>
       <c r="R20" t="n">
-        <v>6999814</v>
+        <v>6999862</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800279</v>
+        <v>124800288</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441280</v>
+        <v>441172</v>
       </c>
       <c r="R21" t="n">
-        <v>6999989</v>
+        <v>6999861</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800292</v>
+        <v>124800286</v>
       </c>
       <c r="B22" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441167</v>
+        <v>441175</v>
       </c>
       <c r="R22" t="n">
-        <v>6999862</v>
+        <v>6999877</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800290</v>
+        <v>124800269</v>
       </c>
       <c r="B23" t="n">
-        <v>74906</v>
+        <v>91700</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2913,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1467</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2939,16 +2939,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441172</v>
+        <v>441442</v>
       </c>
       <c r="R23" t="n">
-        <v>6999861</v>
+        <v>6999893</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2983,12 +2986,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3007,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800284</v>
+        <v>124800285</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>74906</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3023,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3051,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441196</v>
+        <v>441184</v>
       </c>
       <c r="R24" t="n">
-        <v>6999904</v>
+        <v>6999878</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,10 +3122,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800288</v>
+        <v>124800289</v>
       </c>
       <c r="B25" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3129,21 +3138,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3160,7 +3169,7 @@
         <v>441172</v>
       </c>
       <c r="R25" t="n">
-        <v>6999861</v>
+        <v>6999878</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800261</v>
+        <v>124800273</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3235,21 +3244,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3263,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441557</v>
+        <v>441403</v>
       </c>
       <c r="R26" t="n">
-        <v>6999865</v>
+        <v>6999822</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800257</v>
+        <v>124800276</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3341,21 +3350,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3369,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441670</v>
+        <v>441381</v>
       </c>
       <c r="R27" t="n">
-        <v>6999866</v>
+        <v>7000012</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800258</v>
+        <v>124800262</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>77753</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3447,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3475,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441578</v>
+        <v>441527</v>
       </c>
       <c r="R28" t="n">
-        <v>6999868</v>
+        <v>6999858</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800275</v>
+        <v>124800290</v>
       </c>
       <c r="B29" t="n">
-        <v>91026</v>
+        <v>74906</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3553,21 +3562,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3581,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441386</v>
+        <v>441172</v>
       </c>
       <c r="R29" t="n">
-        <v>6999830</v>
+        <v>6999861</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800276</v>
+        <v>124800283</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>96354</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3659,21 +3668,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3687,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441381</v>
+        <v>441246</v>
       </c>
       <c r="R30" t="n">
-        <v>7000012</v>
+        <v>6999794</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3749,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800269</v>
+        <v>124800267</v>
       </c>
       <c r="B31" t="n">
-        <v>91700</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3761,25 +3770,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3787,19 +3796,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441442</v>
+        <v>441444</v>
       </c>
       <c r="R31" t="n">
-        <v>6999893</v>
+        <v>6999902</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,18 +3840,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800260</v>
+        <v>124800283</v>
       </c>
       <c r="B2" t="n">
-        <v>91299</v>
+        <v>96354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441560</v>
+        <v>441246</v>
       </c>
       <c r="R2" t="n">
-        <v>6999870</v>
+        <v>6999794</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800257</v>
+        <v>124800269</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>91700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,16 +819,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441670</v>
+        <v>441442</v>
       </c>
       <c r="R3" t="n">
-        <v>6999866</v>
+        <v>6999893</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,12 +866,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800284</v>
+        <v>124800286</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441196</v>
+        <v>441175</v>
       </c>
       <c r="R4" t="n">
-        <v>6999904</v>
+        <v>6999877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +1002,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800266</v>
+        <v>124800263</v>
       </c>
       <c r="B5" t="n">
         <v>74901</v>
@@ -1037,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441484</v>
+        <v>441519</v>
       </c>
       <c r="R5" t="n">
-        <v>6999855</v>
+        <v>6999856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800270</v>
+        <v>124800278</v>
       </c>
       <c r="B6" t="n">
         <v>91030</v>
@@ -1143,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441439</v>
+        <v>441332</v>
       </c>
       <c r="R6" t="n">
-        <v>6999872</v>
+        <v>6999837</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800274</v>
+        <v>124800282</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1230,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441388</v>
+        <v>441251</v>
       </c>
       <c r="R7" t="n">
-        <v>6999825</v>
+        <v>6999814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1320,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800261</v>
+        <v>124800257</v>
       </c>
       <c r="B8" t="n">
         <v>91012</v>
@@ -1355,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441557</v>
+        <v>441670</v>
       </c>
       <c r="R8" t="n">
-        <v>6999865</v>
+        <v>6999866</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800258</v>
+        <v>124800285</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>74906</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1442,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441578</v>
+        <v>441184</v>
       </c>
       <c r="R9" t="n">
-        <v>6999868</v>
+        <v>6999878</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800278</v>
+        <v>124800261</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1548,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441332</v>
+        <v>441557</v>
       </c>
       <c r="R10" t="n">
-        <v>6999837</v>
+        <v>6999865</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800279</v>
+        <v>124800284</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1673,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441280</v>
+        <v>441196</v>
       </c>
       <c r="R11" t="n">
-        <v>6999989</v>
+        <v>6999904</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800292</v>
+        <v>124800273</v>
       </c>
       <c r="B12" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1760,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441167</v>
+        <v>441403</v>
       </c>
       <c r="R12" t="n">
-        <v>6999862</v>
+        <v>6999822</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800277</v>
+        <v>124800281</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1866,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1885,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441332</v>
+        <v>441261</v>
       </c>
       <c r="R13" t="n">
-        <v>6999837</v>
+        <v>6999970</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800281</v>
+        <v>124800279</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1972,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1991,10 +2000,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441261</v>
+        <v>441280</v>
       </c>
       <c r="R14" t="n">
-        <v>6999970</v>
+        <v>6999989</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800282</v>
+        <v>124800266</v>
       </c>
       <c r="B15" t="n">
-        <v>96354</v>
+        <v>74901</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2078,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2097,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441251</v>
+        <v>441484</v>
       </c>
       <c r="R15" t="n">
-        <v>6999814</v>
+        <v>6999855</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800287</v>
+        <v>124800291</v>
       </c>
       <c r="B16" t="n">
-        <v>79920</v>
+        <v>74885</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2203,10 +2212,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441173</v>
+        <v>441167</v>
       </c>
       <c r="R16" t="n">
-        <v>6999874</v>
+        <v>6999845</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800263</v>
+        <v>124800267</v>
       </c>
       <c r="B17" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2290,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2309,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441519</v>
+        <v>441444</v>
       </c>
       <c r="R17" t="n">
-        <v>6999856</v>
+        <v>6999902</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800291</v>
+        <v>124800274</v>
       </c>
       <c r="B18" t="n">
-        <v>74885</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2392,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2415,10 +2424,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441167</v>
+        <v>441388</v>
       </c>
       <c r="R18" t="n">
-        <v>6999845</v>
+        <v>6999825</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800275</v>
+        <v>124800289</v>
       </c>
       <c r="B19" t="n">
-        <v>91026</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2502,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2521,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441386</v>
+        <v>441172</v>
       </c>
       <c r="R19" t="n">
-        <v>6999830</v>
+        <v>6999878</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2592,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800264</v>
+        <v>124800258</v>
       </c>
       <c r="B20" t="n">
-        <v>91026</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2608,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2627,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441499</v>
+        <v>441578</v>
       </c>
       <c r="R20" t="n">
-        <v>6999862</v>
+        <v>6999868</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800288</v>
+        <v>124800290</v>
       </c>
       <c r="B21" t="n">
-        <v>74901</v>
+        <v>74906</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2714,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2795,10 +2804,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800286</v>
+        <v>124800287</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>79920</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2816,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2839,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441175</v>
+        <v>441173</v>
       </c>
       <c r="R22" t="n">
-        <v>6999877</v>
+        <v>6999874</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800269</v>
+        <v>124800275</v>
       </c>
       <c r="B23" t="n">
-        <v>91700</v>
+        <v>91026</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2922,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2939,19 +2948,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441442</v>
+        <v>441386</v>
       </c>
       <c r="R23" t="n">
-        <v>6999893</v>
+        <v>6999830</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2986,18 +2992,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800285</v>
+        <v>124800276</v>
       </c>
       <c r="B24" t="n">
-        <v>74906</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3032,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441184</v>
+        <v>441381</v>
       </c>
       <c r="R24" t="n">
-        <v>6999878</v>
+        <v>7000012</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,10 +3122,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800289</v>
+        <v>124800277</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3138,21 +3138,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441172</v>
+        <v>441332</v>
       </c>
       <c r="R25" t="n">
-        <v>6999878</v>
+        <v>6999837</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800273</v>
+        <v>124800264</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,21 +3244,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441403</v>
+        <v>441499</v>
       </c>
       <c r="R26" t="n">
-        <v>6999822</v>
+        <v>6999862</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800276</v>
+        <v>124800292</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3350,21 +3350,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441381</v>
+        <v>441167</v>
       </c>
       <c r="R27" t="n">
-        <v>7000012</v>
+        <v>6999862</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800262</v>
+        <v>124800288</v>
       </c>
       <c r="B28" t="n">
-        <v>77753</v>
+        <v>74901</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>314</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441527</v>
+        <v>441172</v>
       </c>
       <c r="R28" t="n">
-        <v>6999858</v>
+        <v>6999861</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800290</v>
+        <v>124800270</v>
       </c>
       <c r="B29" t="n">
-        <v>74906</v>
+        <v>91030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441172</v>
+        <v>441439</v>
       </c>
       <c r="R29" t="n">
-        <v>6999861</v>
+        <v>6999872</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800283</v>
+        <v>124800262</v>
       </c>
       <c r="B30" t="n">
-        <v>96354</v>
+        <v>77753</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3668,21 +3668,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441246</v>
+        <v>441527</v>
       </c>
       <c r="R30" t="n">
-        <v>6999794</v>
+        <v>6999858</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800267</v>
+        <v>124800260</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441444</v>
+        <v>441560</v>
       </c>
       <c r="R31" t="n">
-        <v>6999902</v>
+        <v>6999870</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800283</v>
+        <v>124800269</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
+        <v>91700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441246</v>
+        <v>441442</v>
       </c>
       <c r="R2" t="n">
-        <v>6999794</v>
+        <v>6999893</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,12 +760,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800269</v>
+        <v>124800283</v>
       </c>
       <c r="B3" t="n">
-        <v>91700</v>
+        <v>96354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,19 +828,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441442</v>
+        <v>441246</v>
       </c>
       <c r="R3" t="n">
-        <v>6999893</v>
+        <v>6999794</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,18 +872,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800269</v>
+        <v>124800275</v>
       </c>
       <c r="B2" t="n">
-        <v>91700</v>
+        <v>91026</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,19 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441442</v>
+        <v>441386</v>
       </c>
       <c r="R2" t="n">
-        <v>6999893</v>
+        <v>6999830</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,18 +757,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800283</v>
+        <v>124800292</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
+        <v>82597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441246</v>
+        <v>441167</v>
       </c>
       <c r="R3" t="n">
-        <v>6999794</v>
+        <v>6999862</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800286</v>
+        <v>124800276</v>
       </c>
       <c r="B4" t="n">
         <v>91030</v>
@@ -940,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441175</v>
+        <v>441381</v>
       </c>
       <c r="R4" t="n">
-        <v>6999877</v>
+        <v>7000012</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1108,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800278</v>
+        <v>124800274</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1152,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441332</v>
+        <v>441388</v>
       </c>
       <c r="R6" t="n">
-        <v>6999837</v>
+        <v>6999825</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800282</v>
+        <v>124800283</v>
       </c>
       <c r="B7" t="n">
         <v>96354</v>
@@ -1258,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441251</v>
+        <v>441246</v>
       </c>
       <c r="R7" t="n">
-        <v>6999814</v>
+        <v>6999794</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800257</v>
+        <v>124800286</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1364,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441670</v>
+        <v>441175</v>
       </c>
       <c r="R8" t="n">
-        <v>6999866</v>
+        <v>6999877</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800285</v>
+        <v>124800281</v>
       </c>
       <c r="B9" t="n">
-        <v>74906</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1470,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441184</v>
+        <v>441261</v>
       </c>
       <c r="R9" t="n">
-        <v>6999878</v>
+        <v>6999970</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1638,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800284</v>
+        <v>124800282</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1682,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441196</v>
+        <v>441251</v>
       </c>
       <c r="R11" t="n">
-        <v>6999904</v>
+        <v>6999814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800273</v>
+        <v>124800257</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1788,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441403</v>
+        <v>441670</v>
       </c>
       <c r="R12" t="n">
-        <v>6999822</v>
+        <v>6999866</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800281</v>
+        <v>124800273</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1894,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441261</v>
+        <v>441403</v>
       </c>
       <c r="R13" t="n">
-        <v>6999970</v>
+        <v>6999822</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2062,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800266</v>
+        <v>124800284</v>
       </c>
       <c r="B15" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2078,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2106,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441484</v>
+        <v>441196</v>
       </c>
       <c r="R15" t="n">
-        <v>6999855</v>
+        <v>6999904</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800291</v>
+        <v>124800285</v>
       </c>
       <c r="B16" t="n">
-        <v>74885</v>
+        <v>74906</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>1467</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2212,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441167</v>
+        <v>441184</v>
       </c>
       <c r="R16" t="n">
-        <v>6999845</v>
+        <v>6999878</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800267</v>
+        <v>124800289</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2318,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441444</v>
+        <v>441172</v>
       </c>
       <c r="R17" t="n">
-        <v>6999902</v>
+        <v>6999878</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800274</v>
+        <v>124800258</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2396,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2424,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441388</v>
+        <v>441578</v>
       </c>
       <c r="R18" t="n">
-        <v>6999825</v>
+        <v>6999868</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800289</v>
+        <v>124800266</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2502,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2530,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441172</v>
+        <v>441484</v>
       </c>
       <c r="R19" t="n">
-        <v>6999878</v>
+        <v>6999855</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800258</v>
+        <v>124800291</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>74885</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2636,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441578</v>
+        <v>441167</v>
       </c>
       <c r="R20" t="n">
-        <v>6999868</v>
+        <v>6999845</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800290</v>
+        <v>124800277</v>
       </c>
       <c r="B21" t="n">
-        <v>74906</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2714,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2742,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441172</v>
+        <v>441332</v>
       </c>
       <c r="R21" t="n">
-        <v>6999861</v>
+        <v>6999837</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2910,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800275</v>
+        <v>124800262</v>
       </c>
       <c r="B23" t="n">
-        <v>91026</v>
+        <v>77753</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2926,21 +2917,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2954,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441386</v>
+        <v>441527</v>
       </c>
       <c r="R23" t="n">
-        <v>6999830</v>
+        <v>6999858</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800276</v>
+        <v>124800260</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3032,21 +3023,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3060,10 +3051,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441381</v>
+        <v>441560</v>
       </c>
       <c r="R24" t="n">
-        <v>7000012</v>
+        <v>6999870</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800277</v>
+        <v>124800269</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>91700</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3134,25 +3125,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3160,16 +3151,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441332</v>
+        <v>441442</v>
       </c>
       <c r="R25" t="n">
-        <v>6999837</v>
+        <v>6999893</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,12 +3198,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800264</v>
+        <v>124800278</v>
       </c>
       <c r="B26" t="n">
-        <v>91026</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,21 +3244,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441499</v>
+        <v>441332</v>
       </c>
       <c r="R26" t="n">
-        <v>6999862</v>
+        <v>6999837</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800292</v>
+        <v>124800264</v>
       </c>
       <c r="B27" t="n">
-        <v>82597</v>
+        <v>91026</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3350,21 +3350,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441167</v>
+        <v>441499</v>
       </c>
       <c r="R27" t="n">
         <v>6999862</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800288</v>
+        <v>124800267</v>
       </c>
       <c r="B28" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441172</v>
+        <v>441444</v>
       </c>
       <c r="R28" t="n">
-        <v>6999861</v>
+        <v>6999902</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800270</v>
+        <v>124800290</v>
       </c>
       <c r="B29" t="n">
-        <v>91030</v>
+        <v>74906</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441439</v>
+        <v>441172</v>
       </c>
       <c r="R29" t="n">
-        <v>6999872</v>
+        <v>6999861</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800262</v>
+        <v>124800288</v>
       </c>
       <c r="B30" t="n">
-        <v>77753</v>
+        <v>74901</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3668,21 +3668,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>314</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441527</v>
+        <v>441172</v>
       </c>
       <c r="R30" t="n">
-        <v>6999858</v>
+        <v>6999861</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800260</v>
+        <v>124800270</v>
       </c>
       <c r="B31" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441560</v>
+        <v>441439</v>
       </c>
       <c r="R31" t="n">
-        <v>6999870</v>
+        <v>6999872</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800275</v>
+        <v>124800292</v>
       </c>
       <c r="B2" t="n">
-        <v>91026</v>
+        <v>82597</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441386</v>
+        <v>441167</v>
       </c>
       <c r="R2" t="n">
-        <v>6999830</v>
+        <v>6999862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800292</v>
+        <v>124800274</v>
       </c>
       <c r="B3" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441167</v>
+        <v>441388</v>
       </c>
       <c r="R3" t="n">
-        <v>6999862</v>
+        <v>6999825</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800276</v>
+        <v>124800283</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>96354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441381</v>
+        <v>441246</v>
       </c>
       <c r="R4" t="n">
-        <v>7000012</v>
+        <v>6999794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800263</v>
+        <v>124800262</v>
       </c>
       <c r="B5" t="n">
-        <v>74901</v>
+        <v>77753</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441519</v>
+        <v>441527</v>
       </c>
       <c r="R5" t="n">
-        <v>6999856</v>
+        <v>6999858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800274</v>
+        <v>124800285</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>74906</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441388</v>
+        <v>441184</v>
       </c>
       <c r="R6" t="n">
-        <v>6999825</v>
+        <v>6999878</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800283</v>
+        <v>124800284</v>
       </c>
       <c r="B7" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441246</v>
+        <v>441196</v>
       </c>
       <c r="R7" t="n">
-        <v>6999794</v>
+        <v>6999904</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800286</v>
+        <v>124800281</v>
       </c>
       <c r="B8" t="n">
         <v>91030</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441175</v>
+        <v>441261</v>
       </c>
       <c r="R8" t="n">
-        <v>6999877</v>
+        <v>6999970</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800281</v>
+        <v>124800263</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441261</v>
+        <v>441519</v>
       </c>
       <c r="R9" t="n">
-        <v>6999970</v>
+        <v>6999856</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800261</v>
+        <v>124800288</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441557</v>
+        <v>441172</v>
       </c>
       <c r="R10" t="n">
-        <v>6999865</v>
+        <v>6999861</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800282</v>
+        <v>124800291</v>
       </c>
       <c r="B11" t="n">
-        <v>96354</v>
+        <v>74885</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441251</v>
+        <v>441167</v>
       </c>
       <c r="R11" t="n">
-        <v>6999814</v>
+        <v>6999845</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800257</v>
+        <v>124800258</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441670</v>
+        <v>441578</v>
       </c>
       <c r="R12" t="n">
-        <v>6999866</v>
+        <v>6999868</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800273</v>
+        <v>124800275</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441403</v>
+        <v>441386</v>
       </c>
       <c r="R13" t="n">
-        <v>6999822</v>
+        <v>6999830</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800279</v>
+        <v>124800257</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441280</v>
+        <v>441670</v>
       </c>
       <c r="R14" t="n">
-        <v>6999989</v>
+        <v>6999866</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800284</v>
+        <v>124800289</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441196</v>
+        <v>441172</v>
       </c>
       <c r="R15" t="n">
-        <v>6999904</v>
+        <v>6999878</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800285</v>
+        <v>124800290</v>
       </c>
       <c r="B16" t="n">
         <v>74906</v>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441184</v>
+        <v>441172</v>
       </c>
       <c r="R16" t="n">
-        <v>6999878</v>
+        <v>6999861</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800289</v>
+        <v>124800264</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>91026</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441172</v>
+        <v>441499</v>
       </c>
       <c r="R17" t="n">
-        <v>6999878</v>
+        <v>6999862</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800258</v>
+        <v>124800269</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>91700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2409,16 +2409,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441578</v>
+        <v>441442</v>
       </c>
       <c r="R18" t="n">
-        <v>6999868</v>
+        <v>6999893</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,12 +2456,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2477,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800266</v>
+        <v>124800277</v>
       </c>
       <c r="B19" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2502,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2521,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441484</v>
+        <v>441332</v>
       </c>
       <c r="R19" t="n">
-        <v>6999855</v>
+        <v>6999837</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2592,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800291</v>
+        <v>124800286</v>
       </c>
       <c r="B20" t="n">
-        <v>74885</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2604,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2627,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441167</v>
+        <v>441175</v>
       </c>
       <c r="R20" t="n">
-        <v>6999845</v>
+        <v>6999877</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800277</v>
+        <v>124800287</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2710,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2733,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441332</v>
+        <v>441173</v>
       </c>
       <c r="R21" t="n">
-        <v>6999837</v>
+        <v>6999874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2804,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800287</v>
+        <v>124800282</v>
       </c>
       <c r="B22" t="n">
-        <v>79920</v>
+        <v>96354</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2816,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2839,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441173</v>
+        <v>441251</v>
       </c>
       <c r="R22" t="n">
-        <v>6999874</v>
+        <v>6999814</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800262</v>
+        <v>124800270</v>
       </c>
       <c r="B23" t="n">
-        <v>77753</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2917,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>314</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2945,10 +2954,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441527</v>
+        <v>441439</v>
       </c>
       <c r="R23" t="n">
-        <v>6999858</v>
+        <v>6999872</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3113,10 +3122,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800269</v>
+        <v>124800267</v>
       </c>
       <c r="B25" t="n">
-        <v>91700</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3125,25 +3134,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3151,19 +3160,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441442</v>
+        <v>441444</v>
       </c>
       <c r="R25" t="n">
-        <v>6999893</v>
+        <v>6999902</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3198,18 +3204,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800278</v>
+        <v>124800273</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,21 +3244,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441332</v>
+        <v>441403</v>
       </c>
       <c r="R26" t="n">
-        <v>6999837</v>
+        <v>6999822</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800264</v>
+        <v>124800278</v>
       </c>
       <c r="B27" t="n">
-        <v>91026</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3350,21 +3350,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441499</v>
+        <v>441332</v>
       </c>
       <c r="R27" t="n">
-        <v>6999862</v>
+        <v>6999837</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800267</v>
+        <v>124800276</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441444</v>
+        <v>441381</v>
       </c>
       <c r="R28" t="n">
-        <v>6999902</v>
+        <v>7000012</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800290</v>
+        <v>124800279</v>
       </c>
       <c r="B29" t="n">
-        <v>74906</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441172</v>
+        <v>441280</v>
       </c>
       <c r="R29" t="n">
-        <v>6999861</v>
+        <v>6999989</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,7 +3652,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800288</v>
+        <v>124800266</v>
       </c>
       <c r="B30" t="n">
         <v>74901</v>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441172</v>
+        <v>441484</v>
       </c>
       <c r="R30" t="n">
-        <v>6999861</v>
+        <v>6999855</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800270</v>
+        <v>124800261</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441439</v>
+        <v>441557</v>
       </c>
       <c r="R31" t="n">
-        <v>6999872</v>
+        <v>6999865</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800274</v>
+        <v>124800287</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441388</v>
+        <v>441173</v>
       </c>
       <c r="R3" t="n">
-        <v>6999825</v>
+        <v>6999874</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800283</v>
+        <v>124800284</v>
       </c>
       <c r="B4" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441246</v>
+        <v>441196</v>
       </c>
       <c r="R4" t="n">
-        <v>6999794</v>
+        <v>6999904</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800262</v>
+        <v>124800258</v>
       </c>
       <c r="B5" t="n">
-        <v>77753</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>314</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441527</v>
+        <v>441578</v>
       </c>
       <c r="R5" t="n">
-        <v>6999858</v>
+        <v>6999868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800285</v>
+        <v>124800263</v>
       </c>
       <c r="B6" t="n">
-        <v>74906</v>
+        <v>74901</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441184</v>
+        <v>441519</v>
       </c>
       <c r="R6" t="n">
-        <v>6999878</v>
+        <v>6999856</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800284</v>
+        <v>124800274</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441196</v>
+        <v>441388</v>
       </c>
       <c r="R7" t="n">
-        <v>6999904</v>
+        <v>6999825</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800281</v>
+        <v>124800260</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441261</v>
+        <v>441560</v>
       </c>
       <c r="R8" t="n">
-        <v>6999970</v>
+        <v>6999870</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800263</v>
+        <v>124800276</v>
       </c>
       <c r="B9" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441519</v>
+        <v>441381</v>
       </c>
       <c r="R9" t="n">
-        <v>6999856</v>
+        <v>7000012</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800288</v>
+        <v>124800278</v>
       </c>
       <c r="B10" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441172</v>
+        <v>441332</v>
       </c>
       <c r="R10" t="n">
-        <v>6999861</v>
+        <v>6999837</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800291</v>
+        <v>124800288</v>
       </c>
       <c r="B11" t="n">
-        <v>74885</v>
+        <v>74901</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441167</v>
+        <v>441172</v>
       </c>
       <c r="R11" t="n">
-        <v>6999845</v>
+        <v>6999861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800258</v>
+        <v>124800291</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>74885</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441578</v>
+        <v>441167</v>
       </c>
       <c r="R12" t="n">
-        <v>6999868</v>
+        <v>6999845</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800275</v>
+        <v>124800261</v>
       </c>
       <c r="B13" t="n">
-        <v>91026</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441386</v>
+        <v>441557</v>
       </c>
       <c r="R13" t="n">
-        <v>6999830</v>
+        <v>6999865</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800257</v>
+        <v>124800277</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441670</v>
+        <v>441332</v>
       </c>
       <c r="R14" t="n">
-        <v>6999866</v>
+        <v>6999837</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800289</v>
+        <v>124800275</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>91026</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441172</v>
+        <v>441386</v>
       </c>
       <c r="R15" t="n">
-        <v>6999878</v>
+        <v>6999830</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800290</v>
+        <v>124800286</v>
       </c>
       <c r="B16" t="n">
-        <v>74906</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441172</v>
+        <v>441175</v>
       </c>
       <c r="R16" t="n">
-        <v>6999861</v>
+        <v>6999877</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800264</v>
+        <v>124800266</v>
       </c>
       <c r="B17" t="n">
-        <v>91026</v>
+        <v>74901</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441499</v>
+        <v>441484</v>
       </c>
       <c r="R17" t="n">
-        <v>6999862</v>
+        <v>6999855</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2486,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800277</v>
+        <v>124800283</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2502,21 +2502,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441332</v>
+        <v>441246</v>
       </c>
       <c r="R19" t="n">
-        <v>6999837</v>
+        <v>6999794</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800286</v>
+        <v>124800289</v>
       </c>
       <c r="B20" t="n">
         <v>91030</v>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441175</v>
+        <v>441172</v>
       </c>
       <c r="R20" t="n">
-        <v>6999877</v>
+        <v>6999878</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800287</v>
+        <v>124800290</v>
       </c>
       <c r="B21" t="n">
-        <v>79920</v>
+        <v>74906</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2710,25 +2710,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441173</v>
+        <v>441172</v>
       </c>
       <c r="R21" t="n">
-        <v>6999874</v>
+        <v>6999861</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,10 +2804,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800282</v>
+        <v>124800257</v>
       </c>
       <c r="B22" t="n">
-        <v>96354</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441251</v>
+        <v>441670</v>
       </c>
       <c r="R22" t="n">
-        <v>6999814</v>
+        <v>6999866</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800270</v>
+        <v>124800262</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>77753</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441439</v>
+        <v>441527</v>
       </c>
       <c r="R23" t="n">
-        <v>6999872</v>
+        <v>6999858</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800260</v>
+        <v>124800285</v>
       </c>
       <c r="B24" t="n">
-        <v>91299</v>
+        <v>74906</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3032,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1467</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441560</v>
+        <v>441184</v>
       </c>
       <c r="R24" t="n">
-        <v>6999870</v>
+        <v>6999878</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,10 +3122,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800267</v>
+        <v>124800282</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3138,21 +3138,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441444</v>
+        <v>441251</v>
       </c>
       <c r="R25" t="n">
-        <v>6999902</v>
+        <v>6999814</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800278</v>
+        <v>124800281</v>
       </c>
       <c r="B27" t="n">
         <v>91030</v>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441332</v>
+        <v>441261</v>
       </c>
       <c r="R27" t="n">
-        <v>6999837</v>
+        <v>6999970</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800276</v>
+        <v>124800279</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441381</v>
+        <v>441280</v>
       </c>
       <c r="R28" t="n">
-        <v>7000012</v>
+        <v>6999989</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800279</v>
+        <v>124800270</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441280</v>
+        <v>441439</v>
       </c>
       <c r="R29" t="n">
-        <v>6999989</v>
+        <v>6999872</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800266</v>
+        <v>124800264</v>
       </c>
       <c r="B30" t="n">
-        <v>74901</v>
+        <v>91026</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3668,21 +3668,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441484</v>
+        <v>441499</v>
       </c>
       <c r="R30" t="n">
-        <v>6999855</v>
+        <v>6999862</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800261</v>
+        <v>124800267</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441557</v>
+        <v>441444</v>
       </c>
       <c r="R31" t="n">
-        <v>6999865</v>
+        <v>6999902</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -2486,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800283</v>
+        <v>124800289</v>
       </c>
       <c r="B19" t="n">
-        <v>96354</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2502,21 +2502,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441246</v>
+        <v>441172</v>
       </c>
       <c r="R19" t="n">
-        <v>6999794</v>
+        <v>6999878</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800289</v>
+        <v>124800290</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>74906</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2608,21 +2608,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2639,7 +2639,7 @@
         <v>441172</v>
       </c>
       <c r="R20" t="n">
-        <v>6999878</v>
+        <v>6999861</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800290</v>
+        <v>124800283</v>
       </c>
       <c r="B21" t="n">
-        <v>74906</v>
+        <v>96354</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2714,21 +2714,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441172</v>
+        <v>441246</v>
       </c>
       <c r="R21" t="n">
-        <v>6999861</v>
+        <v>6999794</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800285</v>
+        <v>124800282</v>
       </c>
       <c r="B24" t="n">
-        <v>74906</v>
+        <v>96354</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3032,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1467</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441184</v>
+        <v>441251</v>
       </c>
       <c r="R24" t="n">
-        <v>6999878</v>
+        <v>6999814</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,10 +3122,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800282</v>
+        <v>124800285</v>
       </c>
       <c r="B25" t="n">
-        <v>96354</v>
+        <v>74906</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3138,21 +3138,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>1467</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441251</v>
+        <v>441184</v>
       </c>
       <c r="R25" t="n">
-        <v>6999814</v>
+        <v>6999878</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -2486,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800289</v>
+        <v>124800283</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>96354</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2502,21 +2502,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441172</v>
+        <v>441246</v>
       </c>
       <c r="R19" t="n">
-        <v>6999878</v>
+        <v>6999794</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800290</v>
+        <v>124800289</v>
       </c>
       <c r="B20" t="n">
-        <v>74906</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2608,21 +2608,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2639,7 +2639,7 @@
         <v>441172</v>
       </c>
       <c r="R20" t="n">
-        <v>6999861</v>
+        <v>6999878</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800283</v>
+        <v>124800290</v>
       </c>
       <c r="B21" t="n">
-        <v>96354</v>
+        <v>74906</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2714,21 +2714,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>1467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441246</v>
+        <v>441172</v>
       </c>
       <c r="R21" t="n">
-        <v>6999794</v>
+        <v>6999861</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800292</v>
+        <v>124800276</v>
       </c>
       <c r="B2" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441167</v>
+        <v>441381</v>
       </c>
       <c r="R2" t="n">
-        <v>6999862</v>
+        <v>7000012</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800287</v>
+        <v>124800273</v>
       </c>
       <c r="B3" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441173</v>
+        <v>441403</v>
       </c>
       <c r="R3" t="n">
-        <v>6999874</v>
+        <v>6999822</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800284</v>
+        <v>124800262</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>77753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441196</v>
+        <v>441527</v>
       </c>
       <c r="R4" t="n">
-        <v>6999904</v>
+        <v>6999858</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800258</v>
+        <v>124800266</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441578</v>
+        <v>441484</v>
       </c>
       <c r="R5" t="n">
-        <v>6999868</v>
+        <v>6999855</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800263</v>
+        <v>124800283</v>
       </c>
       <c r="B6" t="n">
-        <v>74901</v>
+        <v>96354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441519</v>
+        <v>441246</v>
       </c>
       <c r="R6" t="n">
-        <v>6999856</v>
+        <v>6999794</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800274</v>
+        <v>124800267</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441388</v>
+        <v>441444</v>
       </c>
       <c r="R7" t="n">
-        <v>6999825</v>
+        <v>6999902</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800260</v>
+        <v>124800288</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>74901</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441560</v>
+        <v>441172</v>
       </c>
       <c r="R8" t="n">
-        <v>6999870</v>
+        <v>6999861</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800276</v>
+        <v>124800260</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441381</v>
+        <v>441560</v>
       </c>
       <c r="R9" t="n">
-        <v>7000012</v>
+        <v>6999870</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800278</v>
+        <v>124800286</v>
       </c>
       <c r="B10" t="n">
         <v>91030</v>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441332</v>
+        <v>441175</v>
       </c>
       <c r="R10" t="n">
-        <v>6999837</v>
+        <v>6999877</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800288</v>
+        <v>124800289</v>
       </c>
       <c r="B11" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1676,7 +1676,7 @@
         <v>441172</v>
       </c>
       <c r="R11" t="n">
-        <v>6999861</v>
+        <v>6999878</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800291</v>
+        <v>124800274</v>
       </c>
       <c r="B12" t="n">
-        <v>74885</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441167</v>
+        <v>441388</v>
       </c>
       <c r="R12" t="n">
-        <v>6999845</v>
+        <v>6999825</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800261</v>
+        <v>124800263</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441557</v>
+        <v>441519</v>
       </c>
       <c r="R13" t="n">
-        <v>6999865</v>
+        <v>6999856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800277</v>
+        <v>124800284</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441332</v>
+        <v>441196</v>
       </c>
       <c r="R14" t="n">
-        <v>6999837</v>
+        <v>6999904</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800275</v>
+        <v>124800277</v>
       </c>
       <c r="B15" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441386</v>
+        <v>441332</v>
       </c>
       <c r="R15" t="n">
-        <v>6999830</v>
+        <v>6999837</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800286</v>
+        <v>124800258</v>
       </c>
       <c r="B16" t="n">
         <v>91030</v>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441175</v>
+        <v>441578</v>
       </c>
       <c r="R16" t="n">
-        <v>6999877</v>
+        <v>6999868</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800266</v>
+        <v>124800261</v>
       </c>
       <c r="B17" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441484</v>
+        <v>441557</v>
       </c>
       <c r="R17" t="n">
-        <v>6999855</v>
+        <v>6999865</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800269</v>
+        <v>124800279</v>
       </c>
       <c r="B18" t="n">
-        <v>91700</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2409,19 +2409,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441442</v>
+        <v>441280</v>
       </c>
       <c r="R18" t="n">
-        <v>6999893</v>
+        <v>6999989</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,18 +2453,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2486,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800283</v>
+        <v>124800282</v>
       </c>
       <c r="B19" t="n">
         <v>96354</v>
@@ -2530,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441246</v>
+        <v>441251</v>
       </c>
       <c r="R19" t="n">
-        <v>6999794</v>
+        <v>6999814</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800289</v>
+        <v>124800287</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>79920</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2604,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2636,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441172</v>
+        <v>441173</v>
       </c>
       <c r="R20" t="n">
-        <v>6999878</v>
+        <v>6999874</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,7 +2689,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800290</v>
+        <v>124800285</v>
       </c>
       <c r="B21" t="n">
         <v>74906</v>
@@ -2742,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441172</v>
+        <v>441184</v>
       </c>
       <c r="R21" t="n">
-        <v>6999861</v>
+        <v>6999878</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800257</v>
+        <v>124800291</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>74885</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2848,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441670</v>
+        <v>441167</v>
       </c>
       <c r="R22" t="n">
-        <v>6999866</v>
+        <v>6999845</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800262</v>
+        <v>124800278</v>
       </c>
       <c r="B23" t="n">
-        <v>77753</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2926,21 +2917,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>314</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2954,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441527</v>
+        <v>441332</v>
       </c>
       <c r="R23" t="n">
-        <v>6999858</v>
+        <v>6999837</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800282</v>
+        <v>124800292</v>
       </c>
       <c r="B24" t="n">
-        <v>96354</v>
+        <v>82597</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3032,21 +3023,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3060,10 +3051,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441251</v>
+        <v>441167</v>
       </c>
       <c r="R24" t="n">
-        <v>6999814</v>
+        <v>6999862</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800285</v>
+        <v>124800281</v>
       </c>
       <c r="B25" t="n">
-        <v>74906</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3138,21 +3129,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3166,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441184</v>
+        <v>441261</v>
       </c>
       <c r="R25" t="n">
-        <v>6999878</v>
+        <v>6999970</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800273</v>
+        <v>124800290</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>74906</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,21 +3235,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3272,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441403</v>
+        <v>441172</v>
       </c>
       <c r="R26" t="n">
-        <v>6999822</v>
+        <v>6999861</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800281</v>
+        <v>124800275</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>91026</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3350,21 +3341,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3378,10 +3369,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441261</v>
+        <v>441386</v>
       </c>
       <c r="R27" t="n">
-        <v>6999970</v>
+        <v>6999830</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800279</v>
+        <v>124800257</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3456,21 +3447,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3484,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441280</v>
+        <v>441670</v>
       </c>
       <c r="R28" t="n">
-        <v>6999989</v>
+        <v>6999866</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800270</v>
+        <v>124800269</v>
       </c>
       <c r="B29" t="n">
-        <v>91030</v>
+        <v>91700</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3558,25 +3549,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3584,16 +3575,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441439</v>
+        <v>441442</v>
       </c>
       <c r="R29" t="n">
-        <v>6999872</v>
+        <v>6999893</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3628,12 +3622,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800264</v>
+        <v>124800270</v>
       </c>
       <c r="B30" t="n">
-        <v>91026</v>
+        <v>91030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3668,21 +3668,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441499</v>
+        <v>441439</v>
       </c>
       <c r="R30" t="n">
-        <v>6999862</v>
+        <v>6999872</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800267</v>
+        <v>124800264</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441444</v>
+        <v>441499</v>
       </c>
       <c r="R31" t="n">
-        <v>6999902</v>
+        <v>6999862</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800276</v>
+        <v>124800285</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>74906</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441381</v>
+        <v>441184</v>
       </c>
       <c r="R2" t="n">
-        <v>7000012</v>
+        <v>6999878</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800273</v>
+        <v>124800264</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441403</v>
+        <v>441499</v>
       </c>
       <c r="R3" t="n">
-        <v>6999822</v>
+        <v>6999862</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800262</v>
+        <v>124800284</v>
       </c>
       <c r="B4" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441527</v>
+        <v>441196</v>
       </c>
       <c r="R4" t="n">
-        <v>6999858</v>
+        <v>6999904</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800266</v>
+        <v>124800261</v>
       </c>
       <c r="B5" t="n">
-        <v>74901</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441484</v>
+        <v>441557</v>
       </c>
       <c r="R5" t="n">
-        <v>6999855</v>
+        <v>6999865</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800267</v>
+        <v>124800279</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441444</v>
+        <v>441280</v>
       </c>
       <c r="R7" t="n">
-        <v>6999902</v>
+        <v>6999989</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800288</v>
+        <v>124800289</v>
       </c>
       <c r="B8" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1358,7 +1358,7 @@
         <v>441172</v>
       </c>
       <c r="R8" t="n">
-        <v>6999861</v>
+        <v>6999878</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800260</v>
+        <v>124800270</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441560</v>
+        <v>441439</v>
       </c>
       <c r="R9" t="n">
-        <v>6999870</v>
+        <v>6999872</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800286</v>
+        <v>124800262</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>77753</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441175</v>
+        <v>441527</v>
       </c>
       <c r="R10" t="n">
-        <v>6999877</v>
+        <v>6999858</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800289</v>
+        <v>124800273</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441172</v>
+        <v>441403</v>
       </c>
       <c r="R11" t="n">
-        <v>6999878</v>
+        <v>6999822</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800274</v>
+        <v>124800278</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441388</v>
+        <v>441332</v>
       </c>
       <c r="R12" t="n">
-        <v>6999825</v>
+        <v>6999837</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800263</v>
+        <v>124800281</v>
       </c>
       <c r="B13" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441519</v>
+        <v>441261</v>
       </c>
       <c r="R13" t="n">
-        <v>6999856</v>
+        <v>6999970</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800284</v>
+        <v>124800266</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441196</v>
+        <v>441484</v>
       </c>
       <c r="R14" t="n">
-        <v>6999904</v>
+        <v>6999855</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800277</v>
+        <v>124800286</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441332</v>
+        <v>441175</v>
       </c>
       <c r="R15" t="n">
-        <v>6999837</v>
+        <v>6999877</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800258</v>
+        <v>124800282</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>96354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441578</v>
+        <v>441251</v>
       </c>
       <c r="R16" t="n">
-        <v>6999868</v>
+        <v>6999814</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800261</v>
+        <v>124800274</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441557</v>
+        <v>441388</v>
       </c>
       <c r="R17" t="n">
-        <v>6999865</v>
+        <v>6999825</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800279</v>
+        <v>124800275</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441280</v>
+        <v>441386</v>
       </c>
       <c r="R18" t="n">
-        <v>6999989</v>
+        <v>6999830</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800282</v>
+        <v>124800291</v>
       </c>
       <c r="B19" t="n">
-        <v>96354</v>
+        <v>74885</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>6439</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441251</v>
+        <v>441167</v>
       </c>
       <c r="R19" t="n">
-        <v>6999814</v>
+        <v>6999845</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800287</v>
+        <v>124800276</v>
       </c>
       <c r="B20" t="n">
-        <v>79920</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441173</v>
+        <v>441381</v>
       </c>
       <c r="R20" t="n">
-        <v>6999874</v>
+        <v>7000012</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800285</v>
+        <v>124800257</v>
       </c>
       <c r="B21" t="n">
-        <v>74906</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441184</v>
+        <v>441670</v>
       </c>
       <c r="R21" t="n">
-        <v>6999878</v>
+        <v>6999866</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800291</v>
+        <v>124800269</v>
       </c>
       <c r="B22" t="n">
-        <v>74885</v>
+        <v>91700</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6439</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2833,16 +2833,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441167</v>
+        <v>441442</v>
       </c>
       <c r="R22" t="n">
-        <v>6999845</v>
+        <v>6999893</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,12 +2880,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2901,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800278</v>
+        <v>124800292</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2917,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2945,10 +2954,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441332</v>
+        <v>441167</v>
       </c>
       <c r="R23" t="n">
-        <v>6999837</v>
+        <v>6999862</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800292</v>
+        <v>124800258</v>
       </c>
       <c r="B24" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3023,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3051,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441167</v>
+        <v>441578</v>
       </c>
       <c r="R24" t="n">
-        <v>6999862</v>
+        <v>6999868</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,10 +3122,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800281</v>
+        <v>124800290</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>74906</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3129,21 +3138,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3157,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441261</v>
+        <v>441172</v>
       </c>
       <c r="R25" t="n">
-        <v>6999970</v>
+        <v>6999861</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800290</v>
+        <v>124800277</v>
       </c>
       <c r="B26" t="n">
-        <v>74906</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3235,21 +3244,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3263,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441172</v>
+        <v>441332</v>
       </c>
       <c r="R26" t="n">
-        <v>6999861</v>
+        <v>6999837</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800275</v>
+        <v>124800287</v>
       </c>
       <c r="B27" t="n">
-        <v>91026</v>
+        <v>79920</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3337,25 +3346,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3369,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441386</v>
+        <v>441173</v>
       </c>
       <c r="R27" t="n">
-        <v>6999830</v>
+        <v>6999874</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800257</v>
+        <v>124800263</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>74901</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3447,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3475,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441670</v>
+        <v>441519</v>
       </c>
       <c r="R28" t="n">
-        <v>6999866</v>
+        <v>6999856</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800269</v>
+        <v>124800260</v>
       </c>
       <c r="B29" t="n">
-        <v>91700</v>
+        <v>91299</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3549,25 +3558,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3575,19 +3584,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441442</v>
+        <v>441560</v>
       </c>
       <c r="R29" t="n">
-        <v>6999893</v>
+        <v>6999870</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,18 +3628,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800270</v>
+        <v>124800288</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3668,21 +3668,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441439</v>
+        <v>441172</v>
       </c>
       <c r="R30" t="n">
-        <v>6999872</v>
+        <v>6999861</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800264</v>
+        <v>124800267</v>
       </c>
       <c r="B31" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441499</v>
+        <v>441444</v>
       </c>
       <c r="R31" t="n">
-        <v>6999862</v>
+        <v>6999902</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800285</v>
+        <v>124800289</v>
       </c>
       <c r="B2" t="n">
-        <v>74906</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441184</v>
+        <v>441172</v>
       </c>
       <c r="R2" t="n">
         <v>6999878</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800264</v>
+        <v>124800258</v>
       </c>
       <c r="B3" t="n">
-        <v>91026</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441499</v>
+        <v>441578</v>
       </c>
       <c r="R3" t="n">
-        <v>6999862</v>
+        <v>6999868</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800284</v>
+        <v>124800287</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441196</v>
+        <v>441173</v>
       </c>
       <c r="R4" t="n">
-        <v>6999904</v>
+        <v>6999874</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800261</v>
+        <v>124800279</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441557</v>
+        <v>441280</v>
       </c>
       <c r="R5" t="n">
-        <v>6999865</v>
+        <v>6999989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800283</v>
+        <v>124800290</v>
       </c>
       <c r="B6" t="n">
-        <v>96354</v>
+        <v>74906</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441246</v>
+        <v>441172</v>
       </c>
       <c r="R6" t="n">
-        <v>6999794</v>
+        <v>6999861</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800279</v>
+        <v>124800266</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441280</v>
+        <v>441484</v>
       </c>
       <c r="R7" t="n">
-        <v>6999989</v>
+        <v>6999855</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800289</v>
+        <v>124800275</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>91026</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441172</v>
+        <v>441386</v>
       </c>
       <c r="R8" t="n">
-        <v>6999878</v>
+        <v>6999830</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800270</v>
+        <v>124800264</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>91026</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441439</v>
+        <v>441499</v>
       </c>
       <c r="R9" t="n">
-        <v>6999872</v>
+        <v>6999862</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800262</v>
+        <v>124800284</v>
       </c>
       <c r="B10" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441527</v>
+        <v>441196</v>
       </c>
       <c r="R10" t="n">
-        <v>6999858</v>
+        <v>6999904</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800273</v>
+        <v>124800282</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441403</v>
+        <v>441251</v>
       </c>
       <c r="R11" t="n">
-        <v>6999822</v>
+        <v>6999814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800278</v>
+        <v>124800292</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441332</v>
+        <v>441167</v>
       </c>
       <c r="R12" t="n">
-        <v>6999837</v>
+        <v>6999862</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800281</v>
+        <v>124800278</v>
       </c>
       <c r="B13" t="n">
         <v>91030</v>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441261</v>
+        <v>441332</v>
       </c>
       <c r="R13" t="n">
-        <v>6999970</v>
+        <v>6999837</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800266</v>
+        <v>124800262</v>
       </c>
       <c r="B14" t="n">
-        <v>74901</v>
+        <v>77753</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441484</v>
+        <v>441527</v>
       </c>
       <c r="R14" t="n">
-        <v>6999855</v>
+        <v>6999858</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800286</v>
+        <v>124800273</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441175</v>
+        <v>441403</v>
       </c>
       <c r="R15" t="n">
-        <v>6999877</v>
+        <v>6999822</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800282</v>
+        <v>124800274</v>
       </c>
       <c r="B16" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441251</v>
+        <v>441388</v>
       </c>
       <c r="R16" t="n">
-        <v>6999814</v>
+        <v>6999825</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800274</v>
+        <v>124800285</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>74906</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441388</v>
+        <v>441184</v>
       </c>
       <c r="R17" t="n">
-        <v>6999825</v>
+        <v>6999878</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800275</v>
+        <v>124800277</v>
       </c>
       <c r="B18" t="n">
-        <v>91026</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441386</v>
+        <v>441332</v>
       </c>
       <c r="R18" t="n">
-        <v>6999830</v>
+        <v>6999837</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800291</v>
+        <v>124800276</v>
       </c>
       <c r="B19" t="n">
-        <v>74885</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441167</v>
+        <v>441381</v>
       </c>
       <c r="R19" t="n">
-        <v>6999845</v>
+        <v>7000012</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800276</v>
+        <v>124800261</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441381</v>
+        <v>441557</v>
       </c>
       <c r="R20" t="n">
-        <v>7000012</v>
+        <v>6999865</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800257</v>
+        <v>124800270</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441670</v>
+        <v>441439</v>
       </c>
       <c r="R21" t="n">
-        <v>6999866</v>
+        <v>6999872</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800269</v>
+        <v>124800263</v>
       </c>
       <c r="B22" t="n">
-        <v>91700</v>
+        <v>74901</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2833,19 +2833,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441442</v>
+        <v>441519</v>
       </c>
       <c r="R22" t="n">
-        <v>6999893</v>
+        <v>6999856</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,18 +2877,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2910,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800292</v>
+        <v>124800269</v>
       </c>
       <c r="B23" t="n">
-        <v>82597</v>
+        <v>91700</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2922,25 +2913,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2948,16 +2939,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441167</v>
+        <v>441442</v>
       </c>
       <c r="R23" t="n">
-        <v>6999862</v>
+        <v>6999893</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,12 +2986,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800258</v>
+        <v>124800283</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>96354</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3032,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441578</v>
+        <v>441246</v>
       </c>
       <c r="R24" t="n">
-        <v>6999868</v>
+        <v>6999794</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,10 +3122,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800290</v>
+        <v>124800257</v>
       </c>
       <c r="B25" t="n">
-        <v>74906</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3138,21 +3138,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441172</v>
+        <v>441670</v>
       </c>
       <c r="R25" t="n">
-        <v>6999861</v>
+        <v>6999866</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,7 +3228,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800277</v>
+        <v>124800267</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441332</v>
+        <v>441444</v>
       </c>
       <c r="R26" t="n">
-        <v>6999837</v>
+        <v>6999902</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800287</v>
+        <v>124800291</v>
       </c>
       <c r="B27" t="n">
-        <v>79920</v>
+        <v>74885</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3350,21 +3350,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441173</v>
+        <v>441167</v>
       </c>
       <c r="R27" t="n">
-        <v>6999874</v>
+        <v>6999845</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800263</v>
+        <v>124800260</v>
       </c>
       <c r="B28" t="n">
-        <v>74901</v>
+        <v>91299</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441519</v>
+        <v>441560</v>
       </c>
       <c r="R28" t="n">
-        <v>6999856</v>
+        <v>6999870</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800260</v>
+        <v>124800281</v>
       </c>
       <c r="B29" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441560</v>
+        <v>441261</v>
       </c>
       <c r="R29" t="n">
-        <v>6999870</v>
+        <v>6999970</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800267</v>
+        <v>124800286</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441444</v>
+        <v>441175</v>
       </c>
       <c r="R31" t="n">
-        <v>6999902</v>
+        <v>6999877</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800292</v>
+        <v>124800262</v>
       </c>
       <c r="B12" t="n">
-        <v>82597</v>
+        <v>77753</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441167</v>
+        <v>441527</v>
       </c>
       <c r="R12" t="n">
-        <v>6999862</v>
+        <v>6999858</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800278</v>
+        <v>124800273</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441332</v>
+        <v>441403</v>
       </c>
       <c r="R13" t="n">
-        <v>6999837</v>
+        <v>6999822</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800262</v>
+        <v>124800274</v>
       </c>
       <c r="B14" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441527</v>
+        <v>441388</v>
       </c>
       <c r="R14" t="n">
-        <v>6999858</v>
+        <v>6999825</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800273</v>
+        <v>124800278</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441403</v>
+        <v>441332</v>
       </c>
       <c r="R15" t="n">
-        <v>6999822</v>
+        <v>6999837</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800274</v>
+        <v>124800292</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441388</v>
+        <v>441167</v>
       </c>
       <c r="R16" t="n">
-        <v>6999825</v>
+        <v>6999862</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800270</v>
+        <v>124800263</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441439</v>
+        <v>441519</v>
       </c>
       <c r="R21" t="n">
-        <v>6999872</v>
+        <v>6999856</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800263</v>
+        <v>124800270</v>
       </c>
       <c r="B22" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441519</v>
+        <v>441439</v>
       </c>
       <c r="R22" t="n">
-        <v>6999856</v>
+        <v>6999872</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800289</v>
+        <v>124800266</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441172</v>
+        <v>441484</v>
       </c>
       <c r="R2" t="n">
-        <v>6999878</v>
+        <v>6999855</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800258</v>
+        <v>124800292</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441578</v>
+        <v>441167</v>
       </c>
       <c r="R3" t="n">
-        <v>6999868</v>
+        <v>6999862</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800287</v>
+        <v>124800269</v>
       </c>
       <c r="B4" t="n">
-        <v>79920</v>
+        <v>91700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -925,16 +925,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441173</v>
+        <v>441442</v>
       </c>
       <c r="R4" t="n">
-        <v>6999874</v>
+        <v>6999893</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,12 +972,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800279</v>
+        <v>124800263</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441280</v>
+        <v>441519</v>
       </c>
       <c r="R5" t="n">
-        <v>6999989</v>
+        <v>6999856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800290</v>
+        <v>124800276</v>
       </c>
       <c r="B6" t="n">
-        <v>74906</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441172</v>
+        <v>441381</v>
       </c>
       <c r="R6" t="n">
-        <v>6999861</v>
+        <v>7000012</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800266</v>
+        <v>124800290</v>
       </c>
       <c r="B7" t="n">
-        <v>74901</v>
+        <v>74906</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1230,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441484</v>
+        <v>441172</v>
       </c>
       <c r="R7" t="n">
-        <v>6999855</v>
+        <v>6999861</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800275</v>
+        <v>124800260</v>
       </c>
       <c r="B8" t="n">
-        <v>91026</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1336,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441386</v>
+        <v>441560</v>
       </c>
       <c r="R8" t="n">
-        <v>6999830</v>
+        <v>6999870</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800264</v>
+        <v>124800278</v>
       </c>
       <c r="B9" t="n">
-        <v>91026</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1442,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441499</v>
+        <v>441332</v>
       </c>
       <c r="R9" t="n">
-        <v>6999862</v>
+        <v>6999837</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1532,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800284</v>
+        <v>124800273</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1567,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441196</v>
+        <v>441403</v>
       </c>
       <c r="R10" t="n">
-        <v>6999904</v>
+        <v>6999822</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1735,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800262</v>
+        <v>124800267</v>
       </c>
       <c r="B12" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1760,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441527</v>
+        <v>441444</v>
       </c>
       <c r="R12" t="n">
-        <v>6999858</v>
+        <v>6999902</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1850,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800273</v>
+        <v>124800277</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1885,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441403</v>
+        <v>441332</v>
       </c>
       <c r="R13" t="n">
-        <v>6999822</v>
+        <v>6999837</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800274</v>
+        <v>124800258</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1972,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1991,10 +2000,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441388</v>
+        <v>441578</v>
       </c>
       <c r="R14" t="n">
-        <v>6999825</v>
+        <v>6999868</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800278</v>
+        <v>124800285</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>74906</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2078,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2097,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441332</v>
+        <v>441184</v>
       </c>
       <c r="R15" t="n">
-        <v>6999837</v>
+        <v>6999878</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800292</v>
+        <v>124800291</v>
       </c>
       <c r="B16" t="n">
-        <v>82597</v>
+        <v>74885</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,25 +2180,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2206,7 +2215,7 @@
         <v>441167</v>
       </c>
       <c r="R16" t="n">
-        <v>6999862</v>
+        <v>6999845</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800285</v>
+        <v>124800275</v>
       </c>
       <c r="B17" t="n">
-        <v>74906</v>
+        <v>91026</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2290,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2309,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441184</v>
+        <v>441386</v>
       </c>
       <c r="R17" t="n">
-        <v>6999878</v>
+        <v>6999830</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,7 +2380,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800277</v>
+        <v>124800279</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2415,10 +2424,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441332</v>
+        <v>441280</v>
       </c>
       <c r="R18" t="n">
-        <v>6999837</v>
+        <v>6999989</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800276</v>
+        <v>124800261</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2502,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2521,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441381</v>
+        <v>441557</v>
       </c>
       <c r="R19" t="n">
-        <v>7000012</v>
+        <v>6999865</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2592,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800261</v>
+        <v>124800281</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2608,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2627,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441557</v>
+        <v>441261</v>
       </c>
       <c r="R20" t="n">
-        <v>6999865</v>
+        <v>6999970</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800263</v>
+        <v>124800287</v>
       </c>
       <c r="B21" t="n">
-        <v>74901</v>
+        <v>79920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2710,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2733,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441519</v>
+        <v>441173</v>
       </c>
       <c r="R21" t="n">
-        <v>6999856</v>
+        <v>6999874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2804,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800270</v>
+        <v>124800288</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2820,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2839,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441439</v>
+        <v>441172</v>
       </c>
       <c r="R22" t="n">
-        <v>6999872</v>
+        <v>6999861</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800269</v>
+        <v>124800264</v>
       </c>
       <c r="B23" t="n">
-        <v>91700</v>
+        <v>91026</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2922,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2939,19 +2948,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441442</v>
+        <v>441499</v>
       </c>
       <c r="R23" t="n">
-        <v>6999893</v>
+        <v>6999862</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2986,18 +2992,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800283</v>
+        <v>124800257</v>
       </c>
       <c r="B24" t="n">
-        <v>96354</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3032,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441246</v>
+        <v>441670</v>
       </c>
       <c r="R24" t="n">
-        <v>6999794</v>
+        <v>6999866</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,10 +3122,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800257</v>
+        <v>124800262</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>77753</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3138,21 +3138,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441670</v>
+        <v>441527</v>
       </c>
       <c r="R25" t="n">
-        <v>6999866</v>
+        <v>6999858</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800267</v>
+        <v>124800270</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,21 +3244,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441444</v>
+        <v>441439</v>
       </c>
       <c r="R26" t="n">
-        <v>6999902</v>
+        <v>6999872</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800291</v>
+        <v>124800284</v>
       </c>
       <c r="B27" t="n">
-        <v>74885</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3346,25 +3346,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441167</v>
+        <v>441196</v>
       </c>
       <c r="R27" t="n">
-        <v>6999845</v>
+        <v>6999904</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800260</v>
+        <v>124800283</v>
       </c>
       <c r="B28" t="n">
-        <v>91299</v>
+        <v>96354</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441560</v>
+        <v>441246</v>
       </c>
       <c r="R28" t="n">
-        <v>6999870</v>
+        <v>6999794</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800281</v>
+        <v>124800274</v>
       </c>
       <c r="B29" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441261</v>
+        <v>441388</v>
       </c>
       <c r="R29" t="n">
-        <v>6999970</v>
+        <v>6999825</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800288</v>
+        <v>124800286</v>
       </c>
       <c r="B30" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3668,21 +3668,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441172</v>
+        <v>441175</v>
       </c>
       <c r="R30" t="n">
-        <v>6999861</v>
+        <v>6999877</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,7 +3758,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800286</v>
+        <v>124800289</v>
       </c>
       <c r="B31" t="n">
         <v>91030</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441175</v>
+        <v>441172</v>
       </c>
       <c r="R31" t="n">
-        <v>6999877</v>
+        <v>6999878</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -1320,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800260</v>
+        <v>124800278</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,21 +1336,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441560</v>
+        <v>441332</v>
       </c>
       <c r="R8" t="n">
-        <v>6999870</v>
+        <v>6999837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800278</v>
+        <v>124800260</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,21 +1442,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441332</v>
+        <v>441560</v>
       </c>
       <c r="R9" t="n">
-        <v>6999837</v>
+        <v>6999870</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800266</v>
+        <v>124800288</v>
       </c>
       <c r="B2" t="n">
         <v>74901</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441484</v>
+        <v>441172</v>
       </c>
       <c r="R2" t="n">
-        <v>6999855</v>
+        <v>6999861</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800292</v>
+        <v>124800289</v>
       </c>
       <c r="B3" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441167</v>
+        <v>441172</v>
       </c>
       <c r="R3" t="n">
-        <v>6999862</v>
+        <v>6999878</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800269</v>
+        <v>124800278</v>
       </c>
       <c r="B4" t="n">
-        <v>91700</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -925,19 +925,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441442</v>
+        <v>441332</v>
       </c>
       <c r="R4" t="n">
-        <v>6999893</v>
+        <v>6999837</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,18 +969,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1002,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800263</v>
+        <v>124800258</v>
       </c>
       <c r="B5" t="n">
-        <v>74901</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1046,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441519</v>
+        <v>441578</v>
       </c>
       <c r="R5" t="n">
-        <v>6999856</v>
+        <v>6999868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800276</v>
+        <v>124800285</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>74906</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1152,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441381</v>
+        <v>441184</v>
       </c>
       <c r="R6" t="n">
-        <v>7000012</v>
+        <v>6999878</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800290</v>
+        <v>124800266</v>
       </c>
       <c r="B7" t="n">
-        <v>74906</v>
+        <v>74901</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1258,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441172</v>
+        <v>441484</v>
       </c>
       <c r="R7" t="n">
-        <v>6999861</v>
+        <v>6999855</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800278</v>
+        <v>124800283</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>96354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1364,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441332</v>
+        <v>441246</v>
       </c>
       <c r="R8" t="n">
-        <v>6999837</v>
+        <v>6999794</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800260</v>
+        <v>124800263</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>74901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1470,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441560</v>
+        <v>441519</v>
       </c>
       <c r="R9" t="n">
-        <v>6999870</v>
+        <v>6999856</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800273</v>
+        <v>124800292</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1576,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441403</v>
+        <v>441167</v>
       </c>
       <c r="R10" t="n">
-        <v>6999822</v>
+        <v>6999862</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800282</v>
+        <v>124800273</v>
       </c>
       <c r="B11" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1682,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441251</v>
+        <v>441403</v>
       </c>
       <c r="R11" t="n">
-        <v>6999814</v>
+        <v>6999822</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800267</v>
+        <v>124800261</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1788,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441444</v>
+        <v>441557</v>
       </c>
       <c r="R12" t="n">
-        <v>6999902</v>
+        <v>6999865</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800277</v>
+        <v>124800275</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91026</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1894,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441332</v>
+        <v>441386</v>
       </c>
       <c r="R13" t="n">
-        <v>6999837</v>
+        <v>6999830</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800258</v>
+        <v>124800270</v>
       </c>
       <c r="B14" t="n">
         <v>91030</v>
@@ -2000,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441578</v>
+        <v>441439</v>
       </c>
       <c r="R14" t="n">
-        <v>6999868</v>
+        <v>6999872</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800285</v>
+        <v>124800290</v>
       </c>
       <c r="B15" t="n">
         <v>74906</v>
@@ -2106,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441184</v>
+        <v>441172</v>
       </c>
       <c r="R15" t="n">
-        <v>6999878</v>
+        <v>6999861</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800291</v>
+        <v>124800286</v>
       </c>
       <c r="B16" t="n">
-        <v>74885</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2212,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441167</v>
+        <v>441175</v>
       </c>
       <c r="R16" t="n">
-        <v>6999845</v>
+        <v>6999877</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800275</v>
+        <v>124800276</v>
       </c>
       <c r="B17" t="n">
-        <v>91026</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2318,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441386</v>
+        <v>441381</v>
       </c>
       <c r="R17" t="n">
-        <v>6999830</v>
+        <v>7000012</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800279</v>
+        <v>124800260</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2396,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2424,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441280</v>
+        <v>441560</v>
       </c>
       <c r="R18" t="n">
-        <v>6999989</v>
+        <v>6999870</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800261</v>
+        <v>124800257</v>
       </c>
       <c r="B19" t="n">
         <v>91012</v>
@@ -2530,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441557</v>
+        <v>441670</v>
       </c>
       <c r="R19" t="n">
-        <v>6999865</v>
+        <v>6999866</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800281</v>
+        <v>124800274</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2608,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2636,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441261</v>
+        <v>441388</v>
       </c>
       <c r="R20" t="n">
-        <v>6999970</v>
+        <v>6999825</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2804,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800288</v>
+        <v>124800279</v>
       </c>
       <c r="B22" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2820,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2848,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441172</v>
+        <v>441280</v>
       </c>
       <c r="R22" t="n">
-        <v>6999861</v>
+        <v>6999989</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800257</v>
+        <v>124800269</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>91700</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3028,25 +3019,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3054,16 +3045,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441670</v>
+        <v>441442</v>
       </c>
       <c r="R24" t="n">
-        <v>6999866</v>
+        <v>6999893</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3098,12 +3092,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3122,10 +3122,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800262</v>
+        <v>124800267</v>
       </c>
       <c r="B25" t="n">
-        <v>77753</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3138,21 +3138,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441527</v>
+        <v>441444</v>
       </c>
       <c r="R25" t="n">
-        <v>6999858</v>
+        <v>6999902</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800270</v>
+        <v>124800282</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>96354</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,21 +3244,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441439</v>
+        <v>441251</v>
       </c>
       <c r="R26" t="n">
-        <v>6999872</v>
+        <v>6999814</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800284</v>
+        <v>124800281</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3350,21 +3350,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441196</v>
+        <v>441261</v>
       </c>
       <c r="R27" t="n">
-        <v>6999904</v>
+        <v>6999970</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800283</v>
+        <v>124800262</v>
       </c>
       <c r="B28" t="n">
-        <v>96354</v>
+        <v>77753</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441246</v>
+        <v>441527</v>
       </c>
       <c r="R28" t="n">
-        <v>6999794</v>
+        <v>6999858</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800274</v>
+        <v>124800291</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>74885</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3558,25 +3558,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441388</v>
+        <v>441167</v>
       </c>
       <c r="R29" t="n">
-        <v>6999825</v>
+        <v>6999845</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800286</v>
+        <v>124800284</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3668,21 +3668,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441175</v>
+        <v>441196</v>
       </c>
       <c r="R30" t="n">
-        <v>6999877</v>
+        <v>6999904</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800289</v>
+        <v>124800277</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441172</v>
+        <v>441332</v>
       </c>
       <c r="R31" t="n">
-        <v>6999878</v>
+        <v>6999837</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800288</v>
+        <v>124800269</v>
       </c>
       <c r="B2" t="n">
-        <v>74901</v>
+        <v>91860</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441172</v>
+        <v>441442</v>
       </c>
       <c r="R2" t="n">
-        <v>6999861</v>
+        <v>6999893</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,12 +760,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800289</v>
+        <v>124800270</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441172</v>
+        <v>441439</v>
       </c>
       <c r="R3" t="n">
-        <v>6999878</v>
+        <v>6999872</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800278</v>
+        <v>124800273</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441332</v>
+        <v>441403</v>
       </c>
       <c r="R4" t="n">
-        <v>6999837</v>
+        <v>6999822</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800258</v>
+        <v>124800266</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>75025</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441578</v>
+        <v>441484</v>
       </c>
       <c r="R5" t="n">
-        <v>6999868</v>
+        <v>6999855</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800285</v>
+        <v>124800278</v>
       </c>
       <c r="B6" t="n">
-        <v>74906</v>
+        <v>91184</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441184</v>
+        <v>441332</v>
       </c>
       <c r="R6" t="n">
-        <v>6999878</v>
+        <v>6999837</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800266</v>
+        <v>124800279</v>
       </c>
       <c r="B7" t="n">
-        <v>74901</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1230,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441484</v>
+        <v>441280</v>
       </c>
       <c r="R7" t="n">
-        <v>6999855</v>
+        <v>6999989</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800283</v>
+        <v>124800290</v>
       </c>
       <c r="B8" t="n">
-        <v>96354</v>
+        <v>75030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1336,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441246</v>
+        <v>441172</v>
       </c>
       <c r="R8" t="n">
-        <v>6999794</v>
+        <v>6999861</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800263</v>
+        <v>124800292</v>
       </c>
       <c r="B9" t="n">
-        <v>74901</v>
+        <v>82737</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1442,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441519</v>
+        <v>441167</v>
       </c>
       <c r="R9" t="n">
-        <v>6999856</v>
+        <v>6999862</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800292</v>
+        <v>124800276</v>
       </c>
       <c r="B10" t="n">
-        <v>82597</v>
+        <v>91184</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1548,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441167</v>
+        <v>441381</v>
       </c>
       <c r="R10" t="n">
-        <v>6999862</v>
+        <v>7000012</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800273</v>
+        <v>124800260</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>91459</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1654,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1673,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441403</v>
+        <v>441560</v>
       </c>
       <c r="R11" t="n">
-        <v>6999822</v>
+        <v>6999870</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800261</v>
+        <v>124800282</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>96522</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1760,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441557</v>
+        <v>441251</v>
       </c>
       <c r="R12" t="n">
-        <v>6999865</v>
+        <v>6999814</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1853,7 @@
         <v>124800275</v>
       </c>
       <c r="B13" t="n">
-        <v>91026</v>
+        <v>91180</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800270</v>
+        <v>124800264</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>91180</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1972,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1991,10 +2000,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441439</v>
+        <v>441499</v>
       </c>
       <c r="R14" t="n">
-        <v>6999872</v>
+        <v>6999862</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800290</v>
+        <v>124800288</v>
       </c>
       <c r="B15" t="n">
-        <v>74906</v>
+        <v>75025</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2078,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2159,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800286</v>
+        <v>124800258</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,10 +2212,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441175</v>
+        <v>441578</v>
       </c>
       <c r="R16" t="n">
-        <v>6999877</v>
+        <v>6999868</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800276</v>
+        <v>124800257</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>91166</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2290,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2309,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441381</v>
+        <v>441670</v>
       </c>
       <c r="R17" t="n">
-        <v>7000012</v>
+        <v>6999866</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800260</v>
+        <v>124800267</v>
       </c>
       <c r="B18" t="n">
-        <v>91299</v>
+        <v>78947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2396,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2415,10 +2424,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441560</v>
+        <v>441444</v>
       </c>
       <c r="R18" t="n">
-        <v>6999870</v>
+        <v>6999902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800257</v>
+        <v>124800287</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>80057</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2498,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2521,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441670</v>
+        <v>441173</v>
       </c>
       <c r="R19" t="n">
-        <v>6999866</v>
+        <v>6999874</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2592,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800274</v>
+        <v>124800281</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>91184</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2608,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2627,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441388</v>
+        <v>441261</v>
       </c>
       <c r="R20" t="n">
-        <v>6999825</v>
+        <v>6999970</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800287</v>
+        <v>124800285</v>
       </c>
       <c r="B21" t="n">
-        <v>79920</v>
+        <v>75030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2710,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2733,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441173</v>
+        <v>441184</v>
       </c>
       <c r="R21" t="n">
-        <v>6999874</v>
+        <v>6999878</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2804,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800279</v>
+        <v>124800291</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>75009</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2816,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2839,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441280</v>
+        <v>441167</v>
       </c>
       <c r="R22" t="n">
-        <v>6999989</v>
+        <v>6999845</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800264</v>
+        <v>124800289</v>
       </c>
       <c r="B23" t="n">
-        <v>91026</v>
+        <v>91184</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2917,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2945,10 +2954,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441499</v>
+        <v>441172</v>
       </c>
       <c r="R23" t="n">
-        <v>6999862</v>
+        <v>6999878</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800269</v>
+        <v>124800262</v>
       </c>
       <c r="B24" t="n">
-        <v>91700</v>
+        <v>77889</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,25 +3028,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3045,19 +3054,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441442</v>
+        <v>441527</v>
       </c>
       <c r="R24" t="n">
-        <v>6999893</v>
+        <v>6999858</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3092,18 +3098,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3122,10 +3122,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800267</v>
+        <v>124800286</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>91184</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3138,21 +3138,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441444</v>
+        <v>441175</v>
       </c>
       <c r="R25" t="n">
-        <v>6999902</v>
+        <v>6999877</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800282</v>
+        <v>124800261</v>
       </c>
       <c r="B26" t="n">
-        <v>96354</v>
+        <v>91166</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,21 +3244,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441251</v>
+        <v>441557</v>
       </c>
       <c r="R26" t="n">
-        <v>6999814</v>
+        <v>6999865</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800281</v>
+        <v>124800263</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>75025</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3350,21 +3350,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441261</v>
+        <v>441519</v>
       </c>
       <c r="R27" t="n">
-        <v>6999970</v>
+        <v>6999856</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800262</v>
+        <v>124800277</v>
       </c>
       <c r="B28" t="n">
-        <v>77753</v>
+        <v>78947</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441527</v>
+        <v>441332</v>
       </c>
       <c r="R28" t="n">
-        <v>6999858</v>
+        <v>6999837</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800291</v>
+        <v>124800284</v>
       </c>
       <c r="B29" t="n">
-        <v>74885</v>
+        <v>78947</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3558,25 +3558,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441167</v>
+        <v>441196</v>
       </c>
       <c r="R29" t="n">
-        <v>6999845</v>
+        <v>6999904</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800284</v>
+        <v>124800274</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441196</v>
+        <v>441388</v>
       </c>
       <c r="R30" t="n">
-        <v>6999904</v>
+        <v>6999825</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800277</v>
+        <v>124800283</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>96522</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441332</v>
+        <v>441246</v>
       </c>
       <c r="R31" t="n">
-        <v>6999837</v>
+        <v>6999794</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -2486,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800287</v>
+        <v>124800281</v>
       </c>
       <c r="B19" t="n">
-        <v>80057</v>
+        <v>91184</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,25 +2498,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441173</v>
+        <v>441261</v>
       </c>
       <c r="R19" t="n">
-        <v>6999874</v>
+        <v>6999970</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800281</v>
+        <v>124800285</v>
       </c>
       <c r="B20" t="n">
-        <v>91184</v>
+        <v>75030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2608,21 +2608,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441261</v>
+        <v>441184</v>
       </c>
       <c r="R20" t="n">
-        <v>6999970</v>
+        <v>6999878</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800285</v>
+        <v>124800287</v>
       </c>
       <c r="B21" t="n">
-        <v>75030</v>
+        <v>80057</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2710,25 +2710,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441184</v>
+        <v>441173</v>
       </c>
       <c r="R21" t="n">
-        <v>6999878</v>
+        <v>6999874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,10 +2804,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800291</v>
+        <v>124800289</v>
       </c>
       <c r="B22" t="n">
-        <v>75009</v>
+        <v>91184</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,25 +2816,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441167</v>
+        <v>441172</v>
       </c>
       <c r="R22" t="n">
-        <v>6999845</v>
+        <v>6999878</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800289</v>
+        <v>124800262</v>
       </c>
       <c r="B23" t="n">
-        <v>91184</v>
+        <v>77889</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441172</v>
+        <v>441527</v>
       </c>
       <c r="R23" t="n">
-        <v>6999878</v>
+        <v>6999858</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800262</v>
+        <v>124800291</v>
       </c>
       <c r="B24" t="n">
-        <v>77889</v>
+        <v>75009</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3028,25 +3028,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>314</v>
+        <v>6439</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441527</v>
+        <v>441167</v>
       </c>
       <c r="R24" t="n">
-        <v>6999858</v>
+        <v>6999845</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800277</v>
+        <v>124800283</v>
       </c>
       <c r="B28" t="n">
-        <v>78947</v>
+        <v>96522</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441332</v>
+        <v>441246</v>
       </c>
       <c r="R28" t="n">
-        <v>6999837</v>
+        <v>6999794</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800284</v>
+        <v>124800277</v>
       </c>
       <c r="B29" t="n">
         <v>78947</v>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441196</v>
+        <v>441332</v>
       </c>
       <c r="R29" t="n">
-        <v>6999904</v>
+        <v>6999837</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,7 +3652,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800274</v>
+        <v>124800284</v>
       </c>
       <c r="B30" t="n">
         <v>78947</v>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441388</v>
+        <v>441196</v>
       </c>
       <c r="R30" t="n">
-        <v>6999825</v>
+        <v>6999904</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800283</v>
+        <v>124800274</v>
       </c>
       <c r="B31" t="n">
-        <v>96522</v>
+        <v>78947</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441246</v>
+        <v>441388</v>
       </c>
       <c r="R31" t="n">
-        <v>6999794</v>
+        <v>6999825</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800269</v>
+        <v>124800266</v>
       </c>
       <c r="B2" t="n">
-        <v>91860</v>
+        <v>75025</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,19 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441442</v>
+        <v>441484</v>
       </c>
       <c r="R2" t="n">
-        <v>6999893</v>
+        <v>6999855</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,18 +757,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800270</v>
+        <v>124800284</v>
       </c>
       <c r="B3" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441439</v>
+        <v>441196</v>
       </c>
       <c r="R3" t="n">
-        <v>6999872</v>
+        <v>6999904</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800273</v>
+        <v>124800291</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>75009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441403</v>
+        <v>441167</v>
       </c>
       <c r="R4" t="n">
-        <v>6999822</v>
+        <v>6999845</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800266</v>
+        <v>124800288</v>
       </c>
       <c r="B5" t="n">
         <v>75025</v>
@@ -1046,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441484</v>
+        <v>441172</v>
       </c>
       <c r="R5" t="n">
-        <v>6999855</v>
+        <v>6999861</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800278</v>
+        <v>124800264</v>
       </c>
       <c r="B6" t="n">
-        <v>91184</v>
+        <v>91180</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1152,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441332</v>
+        <v>441499</v>
       </c>
       <c r="R6" t="n">
-        <v>6999837</v>
+        <v>6999862</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800279</v>
+        <v>124800282</v>
       </c>
       <c r="B7" t="n">
-        <v>78947</v>
+        <v>96522</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1258,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441280</v>
+        <v>441251</v>
       </c>
       <c r="R7" t="n">
-        <v>6999989</v>
+        <v>6999814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800290</v>
+        <v>124800262</v>
       </c>
       <c r="B8" t="n">
-        <v>75030</v>
+        <v>77889</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1364,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441172</v>
+        <v>441527</v>
       </c>
       <c r="R8" t="n">
-        <v>6999861</v>
+        <v>6999858</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800292</v>
+        <v>124800287</v>
       </c>
       <c r="B9" t="n">
-        <v>82737</v>
+        <v>80057</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1470,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441167</v>
+        <v>441173</v>
       </c>
       <c r="R9" t="n">
-        <v>6999862</v>
+        <v>6999874</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800276</v>
+        <v>124800277</v>
       </c>
       <c r="B10" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1576,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441381</v>
+        <v>441332</v>
       </c>
       <c r="R10" t="n">
-        <v>7000012</v>
+        <v>6999837</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800260</v>
+        <v>124800281</v>
       </c>
       <c r="B11" t="n">
-        <v>91459</v>
+        <v>91184</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1682,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441560</v>
+        <v>441261</v>
       </c>
       <c r="R11" t="n">
-        <v>6999870</v>
+        <v>6999970</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800282</v>
+        <v>124800269</v>
       </c>
       <c r="B12" t="n">
-        <v>96522</v>
+        <v>91860</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1782,16 +1773,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441251</v>
+        <v>441442</v>
       </c>
       <c r="R12" t="n">
-        <v>6999814</v>
+        <v>6999893</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,12 +1820,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800275</v>
+        <v>124800290</v>
       </c>
       <c r="B13" t="n">
-        <v>91180</v>
+        <v>75030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441386</v>
+        <v>441172</v>
       </c>
       <c r="R13" t="n">
-        <v>6999830</v>
+        <v>6999861</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800264</v>
+        <v>124800258</v>
       </c>
       <c r="B14" t="n">
-        <v>91180</v>
+        <v>91184</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1972,21 +1972,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2000,10 +2000,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441499</v>
+        <v>441578</v>
       </c>
       <c r="R14" t="n">
-        <v>6999862</v>
+        <v>6999868</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800288</v>
+        <v>124800257</v>
       </c>
       <c r="B15" t="n">
-        <v>75025</v>
+        <v>91166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2078,21 +2078,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441172</v>
+        <v>441670</v>
       </c>
       <c r="R15" t="n">
-        <v>6999861</v>
+        <v>6999866</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800258</v>
+        <v>124800289</v>
       </c>
       <c r="B16" t="n">
         <v>91184</v>
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441578</v>
+        <v>441172</v>
       </c>
       <c r="R16" t="n">
-        <v>6999868</v>
+        <v>6999878</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800257</v>
+        <v>124800274</v>
       </c>
       <c r="B17" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,21 +2290,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441670</v>
+        <v>441388</v>
       </c>
       <c r="R17" t="n">
-        <v>6999866</v>
+        <v>6999825</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,10 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800267</v>
+        <v>124800283</v>
       </c>
       <c r="B18" t="n">
-        <v>78947</v>
+        <v>96522</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2396,21 +2396,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441444</v>
+        <v>441246</v>
       </c>
       <c r="R18" t="n">
-        <v>6999902</v>
+        <v>6999794</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800281</v>
+        <v>124800292</v>
       </c>
       <c r="B19" t="n">
-        <v>91184</v>
+        <v>82737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2502,21 +2502,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441261</v>
+        <v>441167</v>
       </c>
       <c r="R19" t="n">
-        <v>6999970</v>
+        <v>6999862</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800285</v>
+        <v>124800273</v>
       </c>
       <c r="B20" t="n">
-        <v>75030</v>
+        <v>78947</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2608,21 +2608,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441184</v>
+        <v>441403</v>
       </c>
       <c r="R20" t="n">
-        <v>6999878</v>
+        <v>6999822</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800287</v>
+        <v>124800278</v>
       </c>
       <c r="B21" t="n">
-        <v>80057</v>
+        <v>91184</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2710,25 +2710,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441173</v>
+        <v>441332</v>
       </c>
       <c r="R21" t="n">
-        <v>6999874</v>
+        <v>6999837</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,10 +2804,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800289</v>
+        <v>124800261</v>
       </c>
       <c r="B22" t="n">
-        <v>91184</v>
+        <v>91166</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441172</v>
+        <v>441557</v>
       </c>
       <c r="R22" t="n">
-        <v>6999878</v>
+        <v>6999865</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800262</v>
+        <v>124800267</v>
       </c>
       <c r="B23" t="n">
-        <v>77889</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441527</v>
+        <v>441444</v>
       </c>
       <c r="R23" t="n">
-        <v>6999858</v>
+        <v>6999902</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800291</v>
+        <v>124800286</v>
       </c>
       <c r="B24" t="n">
-        <v>75009</v>
+        <v>91184</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3028,25 +3028,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441167</v>
+        <v>441175</v>
       </c>
       <c r="R24" t="n">
-        <v>6999845</v>
+        <v>6999877</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,10 +3122,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124800286</v>
+        <v>124800285</v>
       </c>
       <c r="B25" t="n">
-        <v>91184</v>
+        <v>75030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3138,21 +3138,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>441175</v>
+        <v>441184</v>
       </c>
       <c r="R25" t="n">
-        <v>6999877</v>
+        <v>6999878</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124800261</v>
+        <v>124800279</v>
       </c>
       <c r="B26" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,21 +3244,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>441557</v>
+        <v>441280</v>
       </c>
       <c r="R26" t="n">
-        <v>6999865</v>
+        <v>6999989</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124800263</v>
+        <v>124800260</v>
       </c>
       <c r="B27" t="n">
-        <v>75025</v>
+        <v>91459</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3350,21 +3350,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>441519</v>
+        <v>441560</v>
       </c>
       <c r="R27" t="n">
-        <v>6999856</v>
+        <v>6999870</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124800283</v>
+        <v>124800276</v>
       </c>
       <c r="B28" t="n">
-        <v>96522</v>
+        <v>91184</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>441246</v>
+        <v>441381</v>
       </c>
       <c r="R28" t="n">
-        <v>6999794</v>
+        <v>7000012</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124800277</v>
+        <v>124800263</v>
       </c>
       <c r="B29" t="n">
-        <v>78947</v>
+        <v>75025</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>441332</v>
+        <v>441519</v>
       </c>
       <c r="R29" t="n">
-        <v>6999837</v>
+        <v>6999856</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124800284</v>
+        <v>124800275</v>
       </c>
       <c r="B30" t="n">
-        <v>78947</v>
+        <v>91180</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3668,21 +3668,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>441196</v>
+        <v>441386</v>
       </c>
       <c r="R30" t="n">
-        <v>6999904</v>
+        <v>6999830</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124800274</v>
+        <v>124800270</v>
       </c>
       <c r="B31" t="n">
-        <v>78947</v>
+        <v>91184</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>441388</v>
+        <v>441439</v>
       </c>
       <c r="R31" t="n">
-        <v>6999825</v>
+        <v>6999872</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -2592,10 +2592,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800273</v>
+        <v>124800261</v>
       </c>
       <c r="B20" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2608,21 +2608,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441403</v>
+        <v>441557</v>
       </c>
       <c r="R20" t="n">
-        <v>6999822</v>
+        <v>6999865</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2804,10 +2804,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800261</v>
+        <v>124800273</v>
       </c>
       <c r="B22" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441557</v>
+        <v>441403</v>
       </c>
       <c r="R22" t="n">
-        <v>6999865</v>
+        <v>6999822</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124800266</v>
+        <v>124800282</v>
       </c>
       <c r="B2" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441484</v>
+        <v>441251</v>
       </c>
       <c r="R2" t="n">
-        <v>6999855</v>
+        <v>6999814</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124800284</v>
+        <v>124800283</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441196</v>
+        <v>441246</v>
       </c>
       <c r="R3" t="n">
-        <v>6999904</v>
+        <v>6999794</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124800291</v>
+        <v>124800262</v>
       </c>
       <c r="B4" t="n">
-        <v>75009</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441167</v>
+        <v>441527</v>
       </c>
       <c r="R4" t="n">
-        <v>6999845</v>
+        <v>6999858</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124800288</v>
+        <v>124800260</v>
       </c>
       <c r="B5" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441172</v>
+        <v>441560</v>
       </c>
       <c r="R5" t="n">
-        <v>6999861</v>
+        <v>6999870</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124800264</v>
+        <v>124800257</v>
       </c>
       <c r="B6" t="n">
-        <v>91180</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441499</v>
+        <v>441670</v>
       </c>
       <c r="R6" t="n">
-        <v>6999862</v>
+        <v>6999866</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124800282</v>
+        <v>124800261</v>
       </c>
       <c r="B7" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441251</v>
+        <v>441557</v>
       </c>
       <c r="R7" t="n">
-        <v>6999814</v>
+        <v>6999865</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124800262</v>
+        <v>124800264</v>
       </c>
       <c r="B8" t="n">
-        <v>77889</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>314</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441527</v>
+        <v>441499</v>
       </c>
       <c r="R8" t="n">
-        <v>6999858</v>
+        <v>6999862</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124800287</v>
+        <v>124800275</v>
       </c>
       <c r="B9" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441173</v>
+        <v>441386</v>
       </c>
       <c r="R9" t="n">
-        <v>6999874</v>
+        <v>6999830</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124800277</v>
+        <v>124800292</v>
       </c>
       <c r="B10" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441332</v>
+        <v>441167</v>
       </c>
       <c r="R10" t="n">
-        <v>6999837</v>
+        <v>6999862</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124800281</v>
+        <v>124800285</v>
       </c>
       <c r="B11" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1673,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441261</v>
+        <v>441184</v>
       </c>
       <c r="R11" t="n">
-        <v>6999970</v>
+        <v>6999878</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,37 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124800269</v>
+        <v>124800290</v>
       </c>
       <c r="B12" t="n">
-        <v>91860</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1773,19 +1718,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441442</v>
+        <v>441172</v>
       </c>
       <c r="R12" t="n">
-        <v>6999893</v>
+        <v>6999861</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,18 +1762,12 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1850,37 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124800290</v>
+        <v>124800269</v>
       </c>
       <c r="B13" t="n">
-        <v>75030</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1467</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1888,16 +1819,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441172</v>
+        <v>441442</v>
       </c>
       <c r="R13" t="n">
-        <v>6999861</v>
+        <v>6999893</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,12 +1866,18 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1956,37 +1896,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124800258</v>
+        <v>124800267</v>
       </c>
       <c r="B14" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2000,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441578</v>
+        <v>441444</v>
       </c>
       <c r="R14" t="n">
-        <v>6999868</v>
+        <v>6999902</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,37 +1997,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124800257</v>
+        <v>124800273</v>
       </c>
       <c r="B15" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2106,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441670</v>
+        <v>441403</v>
       </c>
       <c r="R15" t="n">
-        <v>6999866</v>
+        <v>6999822</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2168,37 +2098,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124800289</v>
+        <v>124800274</v>
       </c>
       <c r="B16" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2212,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441172</v>
+        <v>441388</v>
       </c>
       <c r="R16" t="n">
-        <v>6999878</v>
+        <v>6999825</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,19 +2199,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124800274</v>
+        <v>124800277</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2318,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441388</v>
+        <v>441332</v>
       </c>
       <c r="R17" t="n">
-        <v>6999825</v>
+        <v>6999837</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,37 +2300,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800283</v>
+        <v>124800279</v>
       </c>
       <c r="B18" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2424,10 +2339,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441246</v>
+        <v>441280</v>
       </c>
       <c r="R18" t="n">
-        <v>6999794</v>
+        <v>6999989</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,37 +2401,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800292</v>
+        <v>124800284</v>
       </c>
       <c r="B19" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2530,10 +2440,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441167</v>
+        <v>441196</v>
       </c>
       <c r="R19" t="n">
-        <v>6999862</v>
+        <v>6999904</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,37 +2502,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800261</v>
+        <v>124800291</v>
       </c>
       <c r="B20" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2636,10 +2541,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441557</v>
+        <v>441167</v>
       </c>
       <c r="R20" t="n">
-        <v>6999865</v>
+        <v>6999845</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,15 +2603,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800278</v>
+        <v>124800263</v>
       </c>
       <c r="B21" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2714,21 +2614,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2742,10 +2642,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441332</v>
+        <v>441519</v>
       </c>
       <c r="R21" t="n">
-        <v>6999837</v>
+        <v>6999856</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,15 +2704,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800273</v>
+        <v>124800266</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,21 +2715,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2848,10 +2743,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>441403</v>
+        <v>441484</v>
       </c>
       <c r="R22" t="n">
-        <v>6999822</v>
+        <v>6999855</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,15 +2805,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124800267</v>
+        <v>124800288</v>
       </c>
       <c r="B23" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,21 +2816,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2954,10 +2844,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>441444</v>
+        <v>441172</v>
       </c>
       <c r="R23" t="n">
-        <v>6999902</v>
+        <v>6999861</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,37 +2906,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124800286</v>
+        <v>124800287</v>
       </c>
       <c r="B24" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3060,10 +2945,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>441175</v>
+        <v>441173</v>
       </c>
       <c r="R24" t="n">
-        <v>6999877</v>
+        <v>6999874</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3119,748 +3004,6 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>124800285</v>
-      </c>
-      <c r="B25" t="n">
-        <v>75030</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Rödbrun blekspik</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Sclerophora coniophaea</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Västerfjället, Jmt</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>441184</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6999878</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>124800279</v>
-      </c>
-      <c r="B26" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Västerfjället, Jmt</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>441280</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6999989</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>124800260</v>
-      </c>
-      <c r="B27" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>658</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Västerfjället, Jmt</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>441560</v>
-      </c>
-      <c r="R27" t="n">
-        <v>6999870</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>124800276</v>
-      </c>
-      <c r="B28" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Västerfjället, Jmt</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>441381</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7000012</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>124800263</v>
-      </c>
-      <c r="B29" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Västerfjället, Jmt</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>441519</v>
-      </c>
-      <c r="R29" t="n">
-        <v>6999856</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>124800275</v>
-      </c>
-      <c r="B30" t="n">
-        <v>91180</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Västerfjället, Jmt</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>441386</v>
-      </c>
-      <c r="R30" t="n">
-        <v>6999830</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>124800270</v>
-      </c>
-      <c r="B31" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Västerfjället, Jmt</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>441439</v>
-      </c>
-      <c r="R31" t="n">
-        <v>6999872</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15905-2025 artfynd.xlsx
+++ b/artfynd/A 15905-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800282</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800283</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800262</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800260</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800257</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800261</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800264</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800275</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800292</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800285</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800290</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800269</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1994,6 +2059,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800267</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800273</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2196,6 +2271,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800274</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2297,6 +2377,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800277</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2398,6 +2483,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800279</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2499,6 +2589,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800284</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2600,6 +2695,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800291</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2701,6 +2801,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800263</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2802,6 +2907,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800266</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2903,6 +3013,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800288</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3004,8 +3119,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800287</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>